--- a/tutorials/flex_ro/sweep results/water_targ_sweep_ALL_RESULTS.xlsx
+++ b/tutorials/flex_ro/sweep results/water_targ_sweep_ALL_RESULTS.xlsx
@@ -8,9 +8,10 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rchurchi\watertap\tutorials\flex_ro\sweep results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AC3565F-11BF-4838-AF9A-FB0F5E3F0EF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9868276-1B3B-4482-8D6A-72B457499567}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-6375" yWindow="-21600" windowWidth="14175" windowHeight="20985" firstSheet="1" activeTab="2" xr2:uid="{526C491F-7D81-4CF8-8DF5-6D840C914C1B}"/>
+    <workbookView xWindow="14503" yWindow="0" windowWidth="18497" windowHeight="17880" activeTab="2" xr2:uid="{526C491F-7D81-4CF8-8DF5-6D840C914C1B}"/>
+    <workbookView xWindow="-86" yWindow="0" windowWidth="14760" windowHeight="17880" activeTab="1" xr2:uid="{811D88E6-5E04-4AC4-9B26-930D2EA2E3F2}"/>
   </bookViews>
   <sheets>
     <sheet name="Summer Cost Summary" sheetId="4" r:id="rId1"/>
@@ -92,7 +93,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="27">
   <si>
     <t>Annual AF</t>
   </si>
@@ -292,8 +293,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{61A7BF30-9E2E-4F6C-9DD3-062B2A684BE6}" name="Table1" displayName="Table1" ref="A1:Q33" totalsRowShown="0" headerRowDxfId="2">
-  <autoFilter ref="A1:Q33" xr:uid="{61A7BF30-9E2E-4F6C-9DD3-062B2A684BE6}">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{61A7BF30-9E2E-4F6C-9DD3-062B2A684BE6}" name="Table1" displayName="Table1" ref="A1:Q39" totalsRowShown="0" headerRowDxfId="2">
+  <autoFilter ref="A1:Q39" xr:uid="{61A7BF30-9E2E-4F6C-9DD3-062B2A684BE6}">
     <filterColumn colId="0">
       <filters>
         <filter val="Winter"/>
@@ -301,12 +302,12 @@
     </filterColumn>
     <filterColumn colId="1">
       <filters>
-        <filter val="3"/>
+        <filter val="0"/>
       </filters>
     </filterColumn>
   </autoFilter>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q24">
-    <sortCondition ref="D1:D24"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:Q39">
+    <sortCondition ref="D1:D39"/>
   </sortState>
   <tableColumns count="17">
     <tableColumn id="1" xr3:uid="{FADC07E8-CEDF-4B75-BBE4-A01ACB71EDD0}" name="Season"/>
@@ -619,24 +620,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B1DDFCB-CD48-4284-8222-18B5894FE623}">
   <dimension ref="A1:G21"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="9.23046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.4609375" customWidth="1"/>
-    <col min="4" max="4" width="9.84375" customWidth="1"/>
-    <col min="5" max="5" width="9.4609375" customWidth="1"/>
-    <col min="6" max="6" width="10.3828125" customWidth="1"/>
+    <col min="2" max="2" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.453125" customWidth="1"/>
+    <col min="4" max="4" width="9.81640625" customWidth="1"/>
+    <col min="5" max="5" width="9.453125" customWidth="1"/>
+    <col min="6" max="6" width="10.36328125" customWidth="1"/>
     <col min="7" max="7" width="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="D1" s="6" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="6"/>
       <c r="F1" s="6"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="D2">
         <v>0</v>
       </c>
@@ -647,7 +648,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>0</v>
       </c>
@@ -655,7 +656,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -669,7 +670,7 @@
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B5" s="3">
         <f>C5/$G$10</f>
         <v>1798.4286079070769</v>
@@ -680,7 +681,7 @@
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B6" s="3">
         <f>C6/$G$10</f>
         <v>2397.9615120043568</v>
@@ -690,22 +691,22 @@
       </c>
       <c r="D6" s="1"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="D7" s="1"/>
       <c r="F7" s="1"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="D8" s="1"/>
       <c r="F8" s="1"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="D9" s="1"/>
       <c r="F9" s="1"/>
       <c r="G9" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B10">
         <v>8000</v>
       </c>
@@ -721,7 +722,7 @@
         <v>23.514972912500003</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B11">
         <v>9000</v>
       </c>
@@ -733,7 +734,7 @@
       </c>
       <c r="F11" s="1"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B12" s="3">
         <f>C12/$G$10</f>
         <v>9591.8460480174272</v>
@@ -744,7 +745,7 @@
       <c r="D12" s="1"/>
       <c r="F12" s="1"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B13">
         <v>10000</v>
       </c>
@@ -757,7 +758,7 @@
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B14">
         <v>11000</v>
       </c>
@@ -770,7 +771,7 @@
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B15">
         <v>12000</v>
       </c>
@@ -783,7 +784,7 @@
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B16">
         <v>13000</v>
       </c>
@@ -796,7 +797,7 @@
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B17">
         <v>14000</v>
       </c>
@@ -809,7 +810,7 @@
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B18">
         <v>15000</v>
       </c>
@@ -822,7 +823,7 @@
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="B19">
         <v>16000</v>
       </c>
@@ -835,7 +836,7 @@
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>3</v>
       </c>
@@ -852,7 +853,7 @@
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="C21">
         <f>C20*4/7</f>
         <v>225552</v>
@@ -870,23 +871,23 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E02D5E1-F801-4839-8C05-CA5C31CB2DFA}">
   <dimension ref="B1:H22"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="3" width="9.23046875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.4609375" customWidth="1"/>
-    <col min="5" max="5" width="9.84375" customWidth="1"/>
-    <col min="6" max="6" width="9.4609375" customWidth="1"/>
-    <col min="7" max="7" width="10.3828125" customWidth="1"/>
+    <col min="3" max="3" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.453125" customWidth="1"/>
+    <col min="5" max="5" width="9.81640625" customWidth="1"/>
+    <col min="6" max="6" width="9.453125" customWidth="1"/>
+    <col min="7" max="7" width="10.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:8" x14ac:dyDescent="0.35">
       <c r="E1" s="6" t="s">
         <v>2</v>
       </c>
       <c r="F1" s="6"/>
       <c r="G1" s="6"/>
     </row>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:8" x14ac:dyDescent="0.35">
       <c r="E2">
         <v>0</v>
       </c>
@@ -897,7 +898,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.35">
       <c r="C3" t="s">
         <v>0</v>
       </c>
@@ -905,7 +906,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
         <v>4</v>
       </c>
@@ -921,7 +922,7 @@
         <v>16720.240035535448</v>
       </c>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.35">
       <c r="C5">
         <v>1798</v>
       </c>
@@ -934,7 +935,7 @@
         <v>22368.52857086459</v>
       </c>
     </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:8" x14ac:dyDescent="0.35">
       <c r="C6">
         <v>2398</v>
       </c>
@@ -947,7 +948,7 @@
         <v>28772.571914996501</v>
       </c>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.35">
       <c r="C7">
         <v>3000</v>
       </c>
@@ -956,7 +957,7 @@
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.35">
       <c r="C8">
         <v>4000</v>
       </c>
@@ -969,7 +970,7 @@
       </c>
       <c r="G8" s="1"/>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:8" x14ac:dyDescent="0.35">
       <c r="C9">
         <v>5000</v>
       </c>
@@ -982,7 +983,7 @@
       </c>
       <c r="G9" s="1"/>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.35">
       <c r="C10">
         <v>6000</v>
       </c>
@@ -998,7 +999,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:8" x14ac:dyDescent="0.35">
       <c r="C11">
         <v>7000</v>
       </c>
@@ -1011,12 +1012,15 @@
       </c>
       <c r="G11" s="1"/>
     </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:8" x14ac:dyDescent="0.35">
       <c r="C12">
         <v>8000</v>
       </c>
       <c r="D12" s="3">
         <v>188119.780821792</v>
+      </c>
+      <c r="E12">
+        <v>75507</v>
       </c>
       <c r="F12" s="3">
         <v>80116.314065181752</v>
@@ -1027,7 +1031,7 @@
         <v>23.514972602724001</v>
       </c>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:8" x14ac:dyDescent="0.35">
       <c r="C13">
         <v>9000</v>
       </c>
@@ -1042,7 +1046,7 @@
       </c>
       <c r="G13" s="1"/>
     </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:8" x14ac:dyDescent="0.35">
       <c r="C14" s="3">
         <f>D14/H12</f>
         <v>9591.8461743762273</v>
@@ -1053,35 +1057,47 @@
       <c r="E14" s="1"/>
       <c r="G14" s="1"/>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:8" x14ac:dyDescent="0.35">
       <c r="C15">
         <v>10000</v>
       </c>
+      <c r="E15">
+        <v>93848</v>
+      </c>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="16" spans="2:8" x14ac:dyDescent="0.35">
       <c r="C16">
         <v>11000</v>
       </c>
+      <c r="E16" s="3">
+        <v>102961.15922754805</v>
+      </c>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:7" x14ac:dyDescent="0.35">
       <c r="C17">
         <v>12000</v>
       </c>
+      <c r="E17">
+        <v>112554.99851567688</v>
+      </c>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
     </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:7" x14ac:dyDescent="0.35">
       <c r="C18">
         <v>13000</v>
       </c>
+      <c r="E18" s="3">
+        <v>121344.56621300505</v>
+      </c>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
     </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.35">
       <c r="C19">
         <v>14000</v>
       </c>
@@ -1094,21 +1110,27 @@
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
     </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:7" x14ac:dyDescent="0.35">
       <c r="C20">
         <v>15000</v>
       </c>
+      <c r="E20" s="3">
+        <v>140645.20979357499</v>
+      </c>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
     </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:7" x14ac:dyDescent="0.35">
       <c r="C21">
         <v>16000</v>
       </c>
+      <c r="E21" s="3">
+        <v>149838.83143944858</v>
+      </c>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
     </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="22" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B22" t="s">
         <v>3</v>
       </c>
@@ -1135,28 +1157,28 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44889D92-5C1B-43B6-BE00-3D23C35CC93C}">
-  <dimension ref="A1:Q33"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:Q39"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.69140625" customWidth="1"/>
-    <col min="2" max="3" width="11.84375" customWidth="1"/>
-    <col min="4" max="4" width="22.23046875" customWidth="1"/>
-    <col min="5" max="5" width="28.84375" customWidth="1"/>
-    <col min="6" max="6" width="26.921875" customWidth="1"/>
+    <col min="1" max="1" width="8.7265625" customWidth="1"/>
+    <col min="2" max="3" width="11.81640625" customWidth="1"/>
+    <col min="4" max="4" width="22.26953125" customWidth="1"/>
+    <col min="5" max="5" width="28.81640625" customWidth="1"/>
+    <col min="6" max="6" width="26.90625" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="20.07421875" customWidth="1"/>
-    <col min="9" max="9" width="21.53515625" customWidth="1"/>
-    <col min="10" max="10" width="18.4609375" customWidth="1"/>
-    <col min="11" max="11" width="18.84375" customWidth="1"/>
+    <col min="8" max="8" width="20.08984375" customWidth="1"/>
+    <col min="9" max="9" width="21.54296875" customWidth="1"/>
+    <col min="10" max="10" width="18.453125" customWidth="1"/>
+    <col min="11" max="11" width="18.81640625" customWidth="1"/>
     <col min="12" max="12" width="22" customWidth="1"/>
-    <col min="13" max="13" width="22.53515625" customWidth="1"/>
-    <col min="14" max="14" width="25.3828125" customWidth="1"/>
-    <col min="15" max="15" width="19.15234375" customWidth="1"/>
-    <col min="16" max="16" width="28.61328125" customWidth="1"/>
-    <col min="17" max="17" width="16.23046875" style="3" customWidth="1"/>
+    <col min="13" max="13" width="22.54296875" customWidth="1"/>
+    <col min="14" max="14" width="25.36328125" customWidth="1"/>
+    <col min="15" max="15" width="19.1796875" customWidth="1"/>
+    <col min="16" max="16" width="28.6328125" customWidth="1"/>
+    <col min="17" max="17" width="16.26953125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>18</v>
       </c>
@@ -1209,7 +1231,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>19</v>
       </c>
@@ -1217,7 +1239,7 @@
         <v>0</v>
       </c>
       <c r="C2" s="3">
-        <f t="shared" ref="C2:C24" si="0">N2+M2+L2+K2+J2</f>
+        <f>N2+M2+L2+K2+J2</f>
         <v>158104.1957609462</v>
       </c>
       <c r="D2">
@@ -1263,7 +1285,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -1271,7 +1293,7 @@
         <v>0</v>
       </c>
       <c r="C3" s="3">
-        <f t="shared" si="0"/>
+        <f>N3+M3+L3+K3+J3</f>
         <v>171053.54809522501</v>
       </c>
       <c r="D3">
@@ -1317,7 +1339,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -1325,7 +1347,7 @@
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <f t="shared" si="0"/>
+        <f>N4+M4+L4+K4+J4</f>
         <v>80541.55863</v>
       </c>
       <c r="D4">
@@ -1371,7 +1393,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -1379,7 +1401,7 @@
         <v>0</v>
       </c>
       <c r="C5" s="3">
-        <f t="shared" si="0"/>
+        <f>N5+M5+L5+K5+J5</f>
         <v>90145.456985227414</v>
       </c>
       <c r="D5">
@@ -1425,7 +1447,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -1433,7 +1455,7 @@
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <f t="shared" si="0"/>
+        <f>N6+M6+L6+K6+J6</f>
         <v>99135.784106883366</v>
       </c>
       <c r="D6">
@@ -1479,7 +1501,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -1487,7 +1509,7 @@
         <v>5</v>
       </c>
       <c r="C7" s="3">
-        <f t="shared" si="0"/>
+        <f>N7+M7+L7+K7+J7</f>
         <v>28772.571914996501</v>
       </c>
       <c r="D7">
@@ -1530,7 +1552,7 @@
         <v>2.6406704469603199</v>
       </c>
     </row>
-    <row r="8" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -1538,7 +1560,7 @@
         <v>5</v>
       </c>
       <c r="C8" s="3">
-        <f t="shared" si="0"/>
+        <f>N8+M8+L8+K8+J8</f>
         <v>22368.52857086459</v>
       </c>
       <c r="D8">
@@ -1581,7 +1603,7 @@
         <v>3.36954571208561</v>
       </c>
     </row>
-    <row r="9" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -1589,7 +1611,7 @@
         <v>5</v>
       </c>
       <c r="C9" s="3">
-        <f t="shared" si="0"/>
+        <f>N9+M9+L9+K9+J9</f>
         <v>16720.240035535448</v>
       </c>
       <c r="D9">
@@ -1632,7 +1654,7 @@
         <v>4.8864727960722396</v>
       </c>
     </row>
-    <row r="10" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>21</v>
       </c>
@@ -1640,7 +1662,7 @@
         <v>0</v>
       </c>
       <c r="C10" s="3">
-        <f t="shared" si="0"/>
+        <f>N10+M10+L10+K10+J10</f>
         <v>108042.46335199999</v>
       </c>
       <c r="D10">
@@ -1686,7 +1708,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -1694,7 +1716,7 @@
         <v>3</v>
       </c>
       <c r="C11" s="3">
-        <f t="shared" si="0"/>
+        <f>N11+M11+L11+K11+J11</f>
         <v>41752.231305558547</v>
       </c>
       <c r="D11">
@@ -1737,7 +1759,7 @@
         <v>1.7211299327173799</v>
       </c>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -1745,7 +1767,7 @@
         <v>3</v>
       </c>
       <c r="C12" s="3">
-        <f t="shared" si="0"/>
+        <f>N12+M12+L12+K12+J12</f>
         <v>51495.778789739757</v>
       </c>
       <c r="D12">
@@ -1788,7 +1810,7 @@
         <v>1.45968753918303</v>
       </c>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>19</v>
       </c>
@@ -1796,7 +1818,7 @@
         <v>3</v>
       </c>
       <c r="C13" s="3">
-        <f t="shared" si="0"/>
+        <f>N13+M13+L13+K13+J13</f>
         <v>60724.979693855727</v>
       </c>
       <c r="D13">
@@ -1839,7 +1861,7 @@
         <v>1.2818199310829099</v>
       </c>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>19</v>
       </c>
@@ -1847,7 +1869,7 @@
         <v>3</v>
       </c>
       <c r="C14" s="3">
-        <f t="shared" si="0"/>
+        <f>N14+M14+L14+K14+J14</f>
         <v>70388.430895292957</v>
       </c>
       <c r="D14">
@@ -1890,7 +1912,7 @@
         <v>1.15734642471583</v>
       </c>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>19</v>
       </c>
@@ -1898,7 +1920,7 @@
         <v>3</v>
       </c>
       <c r="C15" s="3">
-        <f t="shared" si="0"/>
+        <f>N15+M15+L15+K15+J15</f>
         <v>80116.314065181752</v>
       </c>
       <c r="D15">
@@ -1941,7 +1963,7 @@
         <v>1.06438923423513</v>
       </c>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>19</v>
       </c>
@@ -1949,7 +1971,7 @@
         <v>3</v>
       </c>
       <c r="C16" s="3">
-        <f t="shared" si="0"/>
+        <f>N16+M16+L16+K16+J16</f>
         <v>90891.797768890829</v>
       </c>
       <c r="D16">
@@ -1992,7 +2014,7 @@
         <v>0.99711288227329198</v>
       </c>
     </row>
-    <row r="17" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -2000,7 +2022,7 @@
         <v>0</v>
       </c>
       <c r="C17" s="3">
-        <f t="shared" si="0"/>
+        <f>N17+M17+L17+K17+J17</f>
         <v>117856.65704778227</v>
       </c>
       <c r="D17">
@@ -2046,7 +2068,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>21</v>
       </c>
@@ -2054,7 +2076,7 @@
         <v>0</v>
       </c>
       <c r="C18" s="3">
-        <f t="shared" si="0"/>
+        <f>N18+M18+L18+K18+J18</f>
         <v>126980.73146875472</v>
       </c>
       <c r="D18">
@@ -2100,7 +2122,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>21</v>
       </c>
@@ -2108,7 +2130,7 @@
         <v>0</v>
       </c>
       <c r="C19" s="3">
-        <f t="shared" si="0"/>
+        <f>N19+M19+L19+K19+J19</f>
         <v>135947.17095224367</v>
       </c>
       <c r="D19">
@@ -2154,7 +2176,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -2162,7 +2184,7 @@
         <v>0</v>
       </c>
       <c r="C20" s="3">
-        <f t="shared" si="0"/>
+        <f>N20+M20+L20+K20+J20</f>
         <v>75506.612155252791</v>
       </c>
       <c r="D20">
@@ -2208,7 +2230,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>19</v>
       </c>
@@ -2216,7 +2238,7 @@
         <v>0</v>
       </c>
       <c r="C21" s="3">
-        <f t="shared" si="0"/>
+        <f>N21+M21+L21+K21+J21</f>
         <v>85155.50909649636</v>
       </c>
       <c r="D21">
@@ -2262,7 +2284,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>21</v>
       </c>
@@ -2270,7 +2292,7 @@
         <v>0</v>
       </c>
       <c r="C22" s="3">
-        <f t="shared" si="0"/>
+        <f>N22+M22+L22+K22+J22</f>
         <v>146231.12922675692</v>
       </c>
       <c r="D22">
@@ -2316,7 +2338,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="23" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>21</v>
       </c>
@@ -2324,7 +2346,7 @@
         <v>0</v>
       </c>
       <c r="C23" s="3">
-        <f t="shared" si="0"/>
+        <f>N23+M23+L23+K23+J23</f>
         <v>159412.81974307698</v>
       </c>
       <c r="D23">
@@ -2370,7 +2392,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="24" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>19</v>
       </c>
@@ -2378,53 +2400,53 @@
         <v>0</v>
       </c>
       <c r="C24" s="3">
-        <f t="shared" si="0"/>
-        <v>130424.39365381806</v>
+        <f>N24+M24+L24+K24+J24</f>
+        <v>93848.445066986911</v>
       </c>
       <c r="D24">
-        <v>14000</v>
+        <v>10000</v>
       </c>
       <c r="E24">
         <v>10</v>
       </c>
       <c r="F24">
-        <v>329240.017626649</v>
+        <v>235174.795346464</v>
       </c>
       <c r="G24">
-        <v>250530.167023805</v>
+        <v>213972.635897431</v>
       </c>
       <c r="H24">
-        <v>20848.0798472356</v>
+        <v>14616.4032867845</v>
       </c>
       <c r="I24">
-        <v>8176.7344208997802</v>
+        <v>6351.5554479330704</v>
       </c>
       <c r="J24">
-        <v>59388.995445909903</v>
+        <v>42435.799224394301</v>
       </c>
       <c r="K24">
-        <v>18034.7176814257</v>
+        <v>12921.0484166359</v>
       </c>
       <c r="L24">
-        <v>22529.657101452402</v>
+        <v>16095.846994802199</v>
       </c>
       <c r="M24">
-        <v>29024.8142681354</v>
+        <v>20967.958734717598</v>
       </c>
       <c r="N24">
-        <v>1446.20915689464</v>
+        <v>1427.7916964369099</v>
       </c>
       <c r="O24">
-        <v>0.25149700598802299</v>
+        <v>0.125748502994011</v>
       </c>
       <c r="P24">
-        <v>0.76093473943346901</v>
+        <v>0.90984510301030797</v>
       </c>
       <c r="Q24" s="3" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>21</v>
       </c>
@@ -2432,7 +2454,7 @@
         <v>0</v>
       </c>
       <c r="C25" s="3">
-        <f t="shared" ref="C25:C33" si="1">N25+M25+L25+K25+J25</f>
+        <f>N25+M25+L25+K25+J25</f>
         <v>81475.122661244794</v>
       </c>
       <c r="D25">
@@ -2478,7 +2500,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="26" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>21</v>
       </c>
@@ -2486,7 +2508,7 @@
         <v>0</v>
       </c>
       <c r="C26" s="3">
-        <f t="shared" si="1"/>
+        <f>N26+M26+L26+K26+J26</f>
         <v>120337.96252123939</v>
       </c>
       <c r="D26">
@@ -2532,7 +2554,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="27" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>21</v>
       </c>
@@ -2540,7 +2562,7 @@
         <v>0</v>
       </c>
       <c r="C27" s="3">
-        <f t="shared" si="1"/>
+        <f>N27+M27+L27+K27+J27</f>
         <v>120337.96252123939</v>
       </c>
       <c r="D27">
@@ -2586,7 +2608,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>21</v>
       </c>
@@ -2594,7 +2616,7 @@
         <v>0</v>
       </c>
       <c r="C28" s="3">
-        <f t="shared" si="1"/>
+        <f>N28+M28+L28+K28+J28</f>
         <v>120337.96252123939</v>
       </c>
       <c r="D28">
@@ -2640,7 +2662,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="29" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>21</v>
       </c>
@@ -2648,7 +2670,7 @@
         <v>0</v>
       </c>
       <c r="C29" s="3">
-        <f t="shared" si="1"/>
+        <f>N29+M29+L29+K29+J29</f>
         <v>121509.10762980059</v>
       </c>
       <c r="D29">
@@ -2694,7 +2716,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="30" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>21</v>
       </c>
@@ -2702,7 +2724,7 @@
         <v>0</v>
       </c>
       <c r="C30" s="3">
-        <f t="shared" si="1"/>
+        <f>N30+M30+L30+K30+J30</f>
         <v>160240.68755374721</v>
       </c>
       <c r="D30">
@@ -2748,7 +2770,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="31" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>21</v>
       </c>
@@ -2756,7 +2778,7 @@
         <v>0</v>
       </c>
       <c r="C31" s="3">
-        <f t="shared" si="1"/>
+        <f>N31+M31+L31+K31+J31</f>
         <v>160240.68755374721</v>
       </c>
       <c r="D31">
@@ -2802,7 +2824,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="32" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>21</v>
       </c>
@@ -2810,7 +2832,7 @@
         <v>0</v>
       </c>
       <c r="C32" s="3">
-        <f t="shared" si="1"/>
+        <f>N32+M32+L32+K32+J32</f>
         <v>160240.68755374721</v>
       </c>
       <c r="D32">
@@ -2856,7 +2878,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="33" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>21</v>
       </c>
@@ -2864,7 +2886,7 @@
         <v>0</v>
       </c>
       <c r="C33" s="3">
-        <f t="shared" si="1"/>
+        <f>N33+M33+L33+K33+J33</f>
         <v>161854.2162878394</v>
       </c>
       <c r="D33">
@@ -2908,6 +2930,328 @@
       </c>
       <c r="Q33" s="3" t="s">
         <v>26</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>19</v>
+      </c>
+      <c r="B34">
+        <v>0</v>
+      </c>
+      <c r="C34" s="3">
+        <f>N34+M34+L34+K34+J34</f>
+        <v>102961.15922754805</v>
+      </c>
+      <c r="D34">
+        <v>11000</v>
+      </c>
+      <c r="E34">
+        <v>10</v>
+      </c>
+      <c r="F34">
+        <v>258664.698630136</v>
+      </c>
+      <c r="G34">
+        <v>223080.13596780499</v>
+      </c>
+      <c r="H34">
+        <v>16558.382878249799</v>
+      </c>
+      <c r="I34">
+        <v>6639.1612289695604</v>
+      </c>
+      <c r="J34">
+        <v>46607.913757927803</v>
+      </c>
+      <c r="K34">
+        <v>14032.947813471899</v>
+      </c>
+      <c r="L34">
+        <v>17689.7477623042</v>
+      </c>
+      <c r="M34">
+        <v>23197.544107219401</v>
+      </c>
+      <c r="N34">
+        <v>1433.00578662475</v>
+      </c>
+      <c r="O34">
+        <v>0.16167664670658599</v>
+      </c>
+      <c r="P34">
+        <v>0.86242976776195501</v>
+      </c>
+      <c r="Q34" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>19</v>
+      </c>
+      <c r="B35">
+        <v>0</v>
+      </c>
+      <c r="C35" s="3">
+        <f>N35+M35+L35+K35+J35</f>
+        <v>112554.99851567688</v>
+      </c>
+      <c r="D35">
+        <v>12000</v>
+      </c>
+      <c r="E35">
+        <v>10</v>
+      </c>
+      <c r="F35">
+        <v>282179.67123287602</v>
+      </c>
+      <c r="H35">
+        <v>18242.5461916684</v>
+      </c>
+      <c r="I35">
+        <f>4852+2606</f>
+        <v>7458</v>
+      </c>
+      <c r="J35">
+        <v>50843.184005923598</v>
+      </c>
+      <c r="K35">
+        <v>15303.798385783</v>
+      </c>
+      <c r="L35">
+        <v>19297.5304894482</v>
+      </c>
+      <c r="M35">
+        <v>25700.648204926601</v>
+      </c>
+      <c r="N35">
+        <v>1409.83742959549</v>
+      </c>
+      <c r="O35">
+        <v>0</v>
+      </c>
+      <c r="P35">
+        <v>0.82464177024617602</v>
+      </c>
+      <c r="Q35" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>19</v>
+      </c>
+      <c r="B36">
+        <v>0</v>
+      </c>
+      <c r="C36" s="3">
+        <f>N36+M36+L36+K36+J36</f>
+        <v>121344.56621300505</v>
+      </c>
+      <c r="D36">
+        <v>13000</v>
+      </c>
+      <c r="E36">
+        <v>10</v>
+      </c>
+      <c r="F36">
+        <v>305700.960485827</v>
+      </c>
+      <c r="G36">
+        <v>241450.33958299199</v>
+      </c>
+      <c r="H36">
+        <v>18893.080794400601</v>
+      </c>
+      <c r="I36">
+        <v>7655.3649078774997</v>
+      </c>
+      <c r="J36">
+        <v>55282.309265125899</v>
+      </c>
+      <c r="K36">
+        <v>17119.793141132199</v>
+      </c>
+      <c r="L36">
+        <v>20947.808947574202</v>
+      </c>
+      <c r="M36">
+        <v>26548.445702278099</v>
+      </c>
+      <c r="N36">
+        <v>1446.20915689464</v>
+      </c>
+      <c r="O36">
+        <v>0.25149700598802299</v>
+      </c>
+      <c r="P36">
+        <v>0.78982525667983905</v>
+      </c>
+      <c r="Q36" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>19</v>
+      </c>
+      <c r="B37">
+        <v>0</v>
+      </c>
+      <c r="C37" s="3">
+        <f>N37+M37+L37+K37+J37</f>
+        <v>130424.39365381806</v>
+      </c>
+      <c r="D37">
+        <v>14000</v>
+      </c>
+      <c r="E37">
+        <v>10</v>
+      </c>
+      <c r="F37">
+        <v>329240.017626649</v>
+      </c>
+      <c r="G37">
+        <v>250530.167023805</v>
+      </c>
+      <c r="H37">
+        <v>20848.0798472356</v>
+      </c>
+      <c r="I37">
+        <v>8176.7344208997802</v>
+      </c>
+      <c r="J37">
+        <v>59388.995445909903</v>
+      </c>
+      <c r="K37">
+        <v>18034.7176814257</v>
+      </c>
+      <c r="L37">
+        <v>22529.657101452402</v>
+      </c>
+      <c r="M37">
+        <v>29024.8142681354</v>
+      </c>
+      <c r="N37">
+        <v>1446.20915689464</v>
+      </c>
+      <c r="O37">
+        <v>0.25149700598802299</v>
+      </c>
+      <c r="P37">
+        <v>0.76093473943346901</v>
+      </c>
+      <c r="Q37" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>19</v>
+      </c>
+      <c r="B38">
+        <v>0</v>
+      </c>
+      <c r="C38" s="3">
+        <f>N38+M38+L38+K38+J38</f>
+        <v>140645.20979357499</v>
+      </c>
+      <c r="D38">
+        <v>15000</v>
+      </c>
+      <c r="E38">
+        <v>10</v>
+      </c>
+      <c r="F38">
+        <v>352724.58906748501</v>
+      </c>
+      <c r="G38">
+        <v>260787.354890861</v>
+      </c>
+      <c r="H38">
+        <v>22262.8898201671</v>
+      </c>
+      <c r="I38">
+        <v>9101.7415334445996</v>
+      </c>
+      <c r="J38">
+        <v>63827.433131782796</v>
+      </c>
+      <c r="K38">
+        <v>19864.653242648001</v>
+      </c>
+      <c r="L38">
+        <v>24178.654635937</v>
+      </c>
+      <c r="M38">
+        <v>31364.631353611701</v>
+      </c>
+      <c r="N38">
+        <v>1409.83742959549</v>
+      </c>
+      <c r="O38">
+        <v>0</v>
+      </c>
+      <c r="P38">
+        <v>0.73935121897885603</v>
+      </c>
+      <c r="Q38" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>19</v>
+      </c>
+      <c r="B39">
+        <v>0</v>
+      </c>
+      <c r="C39" s="3">
+        <f>N39+M39+L39+K39+J39</f>
+        <v>149838.83143944858</v>
+      </c>
+      <c r="D39">
+        <v>16000</v>
+      </c>
+      <c r="E39">
+        <v>10</v>
+      </c>
+      <c r="F39">
+        <v>376239.56164383498</v>
+      </c>
+      <c r="G39">
+        <v>269980.97653673397</v>
+      </c>
+      <c r="H39">
+        <v>24490.5164898455</v>
+      </c>
+      <c r="I39">
+        <v>10012.4603452017</v>
+      </c>
+      <c r="J39">
+        <v>67790.912007917999</v>
+      </c>
+      <c r="K39">
+        <v>20405.064514286099</v>
+      </c>
+      <c r="L39">
+        <v>25730.040652601801</v>
+      </c>
+      <c r="M39">
+        <v>34502.9768350472</v>
+      </c>
+      <c r="N39">
+        <v>1409.83742959549</v>
+      </c>
+      <c r="O39">
+        <v>0</v>
+      </c>
+      <c r="P39">
+        <v>0.71757732056978696</v>
+      </c>
+      <c r="Q39" s="3" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>

--- a/tutorials/flex_ro/sweep results/water_targ_sweep_ALL_RESULTS.xlsx
+++ b/tutorials/flex_ro/sweep results/water_targ_sweep_ALL_RESULTS.xlsx
@@ -1,17 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr hidePivotFieldList="1"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rchurchi\watertap\tutorials\flex_ro\sweep results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9868276-1B3B-4482-8D6A-72B457499567}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA57482E-4594-4EF8-92A5-118B128B7486}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14503" yWindow="0" windowWidth="18497" windowHeight="17880" activeTab="2" xr2:uid="{526C491F-7D81-4CF8-8DF5-6D840C914C1B}"/>
-    <workbookView xWindow="-86" yWindow="0" windowWidth="14760" windowHeight="17880" activeTab="1" xr2:uid="{811D88E6-5E04-4AC4-9B26-930D2EA2E3F2}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="10170" xr2:uid="{811D88E6-5E04-4AC4-9B26-930D2EA2E3F2}"/>
   </bookViews>
   <sheets>
     <sheet name="Summer Cost Summary" sheetId="4" r:id="rId1"/>
@@ -297,12 +296,17 @@
   <autoFilter ref="A1:Q39" xr:uid="{61A7BF30-9E2E-4F6C-9DD3-062B2A684BE6}">
     <filterColumn colId="0">
       <filters>
-        <filter val="Winter"/>
+        <filter val="Summer"/>
       </filters>
     </filterColumn>
     <filterColumn colId="1">
       <filters>
         <filter val="0"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="3">
+      <filters>
+        <filter val="9000"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -730,7 +734,7 @@
         <v>211634.775495949</v>
       </c>
       <c r="D11" s="3">
-        <v>90145.456985227414</v>
+        <v>90280.635276184097</v>
       </c>
       <c r="F11" s="1"/>
     </row>
@@ -1231,7 +1235,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>19</v>
       </c>
@@ -1239,7 +1243,7 @@
         <v>0</v>
       </c>
       <c r="C2" s="3">
-        <f>N2+M2+L2+K2+J2</f>
+        <f t="shared" ref="C2:C39" si="0">N2+M2+L2+K2+J2</f>
         <v>158104.1957609462</v>
       </c>
       <c r="D2">
@@ -1293,7 +1297,7 @@
         <v>0</v>
       </c>
       <c r="C3" s="3">
-        <f>N3+M3+L3+K3+J3</f>
+        <f t="shared" si="0"/>
         <v>171053.54809522501</v>
       </c>
       <c r="D3">
@@ -1347,7 +1351,7 @@
         <v>0</v>
       </c>
       <c r="C4" s="3">
-        <f>N4+M4+L4+K4+J4</f>
+        <f t="shared" si="0"/>
         <v>80541.55863</v>
       </c>
       <c r="D4">
@@ -1393,7 +1397,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -1402,7 +1406,7 @@
       </c>
       <c r="C5" s="3">
         <f>N5+M5+L5+K5+J5</f>
-        <v>90145.456985227414</v>
+        <v>90280.635276184097</v>
       </c>
       <c r="D5">
         <v>9000</v>
@@ -1411,37 +1415,37 @@
         <v>10</v>
       </c>
       <c r="F5">
-        <v>211634.775495949</v>
+        <v>211634.75342465701</v>
       </c>
       <c r="G5">
-        <v>210256.540792755</v>
+        <v>210417.696825046</v>
       </c>
       <c r="H5">
-        <v>14871.657722592799</v>
+        <v>14646.6764757971</v>
       </c>
       <c r="I5">
-        <v>6315.0305970216004</v>
+        <v>8813.4656236474493</v>
       </c>
       <c r="J5">
-        <v>38197.462944573999</v>
+        <v>38471.8456521587</v>
       </c>
       <c r="K5">
-        <v>14447.7282003115</v>
+        <v>12390.141217574101</v>
       </c>
       <c r="L5">
-        <v>14872.6788013735</v>
+        <v>14543.585328987299</v>
       </c>
       <c r="M5">
-        <v>21186.688319614401</v>
+        <v>23460.1420994445</v>
       </c>
       <c r="N5">
-        <v>1440.8987193540199</v>
+        <v>1414.9209780195099</v>
       </c>
       <c r="O5">
-        <v>0.215568862275449</v>
+        <v>3.59281437125748E-2</v>
       </c>
       <c r="P5">
-        <v>0.99348767375321601</v>
+        <v>0.99424925925483998</v>
       </c>
       <c r="Q5" s="3" t="s">
         <v>25</v>
@@ -1455,7 +1459,7 @@
         <v>0</v>
       </c>
       <c r="C6" s="3">
-        <f>N6+M6+L6+K6+J6</f>
+        <f t="shared" si="0"/>
         <v>99135.784106883366</v>
       </c>
       <c r="D6">
@@ -1509,7 +1513,7 @@
         <v>5</v>
       </c>
       <c r="C7" s="3">
-        <f>N7+M7+L7+K7+J7</f>
+        <f t="shared" si="0"/>
         <v>28772.571914996501</v>
       </c>
       <c r="D7">
@@ -1560,7 +1564,7 @@
         <v>5</v>
       </c>
       <c r="C8" s="3">
-        <f>N8+M8+L8+K8+J8</f>
+        <f t="shared" si="0"/>
         <v>22368.52857086459</v>
       </c>
       <c r="D8">
@@ -1611,7 +1615,7 @@
         <v>5</v>
       </c>
       <c r="C9" s="3">
-        <f>N9+M9+L9+K9+J9</f>
+        <f t="shared" si="0"/>
         <v>16720.240035535448</v>
       </c>
       <c r="D9">
@@ -1662,7 +1666,7 @@
         <v>0</v>
       </c>
       <c r="C10" s="3">
-        <f>N10+M10+L10+K10+J10</f>
+        <f t="shared" si="0"/>
         <v>108042.46335199999</v>
       </c>
       <c r="D10">
@@ -1716,7 +1720,7 @@
         <v>3</v>
       </c>
       <c r="C11" s="3">
-        <f>N11+M11+L11+K11+J11</f>
+        <f t="shared" si="0"/>
         <v>41752.231305558547</v>
       </c>
       <c r="D11">
@@ -1767,7 +1771,7 @@
         <v>3</v>
       </c>
       <c r="C12" s="3">
-        <f>N12+M12+L12+K12+J12</f>
+        <f t="shared" si="0"/>
         <v>51495.778789739757</v>
       </c>
       <c r="D12">
@@ -1818,7 +1822,7 @@
         <v>3</v>
       </c>
       <c r="C13" s="3">
-        <f>N13+M13+L13+K13+J13</f>
+        <f t="shared" si="0"/>
         <v>60724.979693855727</v>
       </c>
       <c r="D13">
@@ -1869,7 +1873,7 @@
         <v>3</v>
       </c>
       <c r="C14" s="3">
-        <f>N14+M14+L14+K14+J14</f>
+        <f t="shared" si="0"/>
         <v>70388.430895292957</v>
       </c>
       <c r="D14">
@@ -1920,7 +1924,7 @@
         <v>3</v>
       </c>
       <c r="C15" s="3">
-        <f>N15+M15+L15+K15+J15</f>
+        <f t="shared" si="0"/>
         <v>80116.314065181752</v>
       </c>
       <c r="D15">
@@ -1971,7 +1975,7 @@
         <v>3</v>
       </c>
       <c r="C16" s="3">
-        <f>N16+M16+L16+K16+J16</f>
+        <f t="shared" si="0"/>
         <v>90891.797768890829</v>
       </c>
       <c r="D16">
@@ -2022,7 +2026,7 @@
         <v>0</v>
       </c>
       <c r="C17" s="3">
-        <f>N17+M17+L17+K17+J17</f>
+        <f t="shared" si="0"/>
         <v>117856.65704778227</v>
       </c>
       <c r="D17">
@@ -2076,7 +2080,7 @@
         <v>0</v>
       </c>
       <c r="C18" s="3">
-        <f>N18+M18+L18+K18+J18</f>
+        <f t="shared" si="0"/>
         <v>126980.73146875472</v>
       </c>
       <c r="D18">
@@ -2130,7 +2134,7 @@
         <v>0</v>
       </c>
       <c r="C19" s="3">
-        <f>N19+M19+L19+K19+J19</f>
+        <f t="shared" si="0"/>
         <v>135947.17095224367</v>
       </c>
       <c r="D19">
@@ -2176,7 +2180,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -2184,7 +2188,7 @@
         <v>0</v>
       </c>
       <c r="C20" s="3">
-        <f>N20+M20+L20+K20+J20</f>
+        <f t="shared" si="0"/>
         <v>75506.612155252791</v>
       </c>
       <c r="D20">
@@ -2230,7 +2234,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>19</v>
       </c>
@@ -2238,7 +2242,7 @@
         <v>0</v>
       </c>
       <c r="C21" s="3">
-        <f>N21+M21+L21+K21+J21</f>
+        <f t="shared" si="0"/>
         <v>85155.50909649636</v>
       </c>
       <c r="D21">
@@ -2292,7 +2296,7 @@
         <v>0</v>
       </c>
       <c r="C22" s="3">
-        <f>N22+M22+L22+K22+J22</f>
+        <f t="shared" si="0"/>
         <v>146231.12922675692</v>
       </c>
       <c r="D22">
@@ -2346,7 +2350,7 @@
         <v>0</v>
       </c>
       <c r="C23" s="3">
-        <f>N23+M23+L23+K23+J23</f>
+        <f t="shared" si="0"/>
         <v>159412.81974307698</v>
       </c>
       <c r="D23">
@@ -2392,7 +2396,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>19</v>
       </c>
@@ -2400,7 +2404,7 @@
         <v>0</v>
       </c>
       <c r="C24" s="3">
-        <f>N24+M24+L24+K24+J24</f>
+        <f t="shared" si="0"/>
         <v>93848.445066986911</v>
       </c>
       <c r="D24">
@@ -2454,7 +2458,7 @@
         <v>0</v>
       </c>
       <c r="C25" s="3">
-        <f>N25+M25+L25+K25+J25</f>
+        <f t="shared" si="0"/>
         <v>81475.122661244794</v>
       </c>
       <c r="D25">
@@ -2500,7 +2504,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="26" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>21</v>
       </c>
@@ -2508,7 +2512,7 @@
         <v>0</v>
       </c>
       <c r="C26" s="3">
-        <f>N26+M26+L26+K26+J26</f>
+        <f t="shared" si="0"/>
         <v>120337.96252123939</v>
       </c>
       <c r="D26">
@@ -2562,7 +2566,7 @@
         <v>0</v>
       </c>
       <c r="C27" s="3">
-        <f>N27+M27+L27+K27+J27</f>
+        <f t="shared" si="0"/>
         <v>120337.96252123939</v>
       </c>
       <c r="D27">
@@ -2616,7 +2620,7 @@
         <v>0</v>
       </c>
       <c r="C28" s="3">
-        <f>N28+M28+L28+K28+J28</f>
+        <f t="shared" si="0"/>
         <v>120337.96252123939</v>
       </c>
       <c r="D28">
@@ -2670,7 +2674,7 @@
         <v>0</v>
       </c>
       <c r="C29" s="3">
-        <f>N29+M29+L29+K29+J29</f>
+        <f t="shared" si="0"/>
         <v>121509.10762980059</v>
       </c>
       <c r="D29">
@@ -2724,7 +2728,7 @@
         <v>0</v>
       </c>
       <c r="C30" s="3">
-        <f>N30+M30+L30+K30+J30</f>
+        <f t="shared" si="0"/>
         <v>160240.68755374721</v>
       </c>
       <c r="D30">
@@ -2778,7 +2782,7 @@
         <v>0</v>
       </c>
       <c r="C31" s="3">
-        <f>N31+M31+L31+K31+J31</f>
+        <f t="shared" si="0"/>
         <v>160240.68755374721</v>
       </c>
       <c r="D31">
@@ -2832,7 +2836,7 @@
         <v>0</v>
       </c>
       <c r="C32" s="3">
-        <f>N32+M32+L32+K32+J32</f>
+        <f t="shared" si="0"/>
         <v>160240.68755374721</v>
       </c>
       <c r="D32">
@@ -2886,7 +2890,7 @@
         <v>0</v>
       </c>
       <c r="C33" s="3">
-        <f>N33+M33+L33+K33+J33</f>
+        <f t="shared" si="0"/>
         <v>161854.2162878394</v>
       </c>
       <c r="D33">
@@ -2932,7 +2936,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>19</v>
       </c>
@@ -2940,7 +2944,7 @@
         <v>0</v>
       </c>
       <c r="C34" s="3">
-        <f>N34+M34+L34+K34+J34</f>
+        <f t="shared" si="0"/>
         <v>102961.15922754805</v>
       </c>
       <c r="D34">
@@ -2986,7 +2990,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>19</v>
       </c>
@@ -2994,7 +2998,7 @@
         <v>0</v>
       </c>
       <c r="C35" s="3">
-        <f>N35+M35+L35+K35+J35</f>
+        <f t="shared" si="0"/>
         <v>112554.99851567688</v>
       </c>
       <c r="D35">
@@ -3038,7 +3042,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>19</v>
       </c>
@@ -3046,7 +3050,7 @@
         <v>0</v>
       </c>
       <c r="C36" s="3">
-        <f>N36+M36+L36+K36+J36</f>
+        <f t="shared" si="0"/>
         <v>121344.56621300505</v>
       </c>
       <c r="D36">
@@ -3092,7 +3096,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>19</v>
       </c>
@@ -3100,7 +3104,7 @@
         <v>0</v>
       </c>
       <c r="C37" s="3">
-        <f>N37+M37+L37+K37+J37</f>
+        <f t="shared" si="0"/>
         <v>130424.39365381806</v>
       </c>
       <c r="D37">
@@ -3146,7 +3150,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>19</v>
       </c>
@@ -3154,7 +3158,7 @@
         <v>0</v>
       </c>
       <c r="C38" s="3">
-        <f>N38+M38+L38+K38+J38</f>
+        <f t="shared" si="0"/>
         <v>140645.20979357499</v>
       </c>
       <c r="D38">
@@ -3200,7 +3204,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>19</v>
       </c>
@@ -3208,7 +3212,7 @@
         <v>0</v>
       </c>
       <c r="C39" s="3">
-        <f>N39+M39+L39+K39+J39</f>
+        <f t="shared" si="0"/>
         <v>149838.83143944858</v>
       </c>
       <c r="D39">

--- a/tutorials/flex_ro/sweep results/water_targ_sweep_ALL_RESULTS.xlsx
+++ b/tutorials/flex_ro/sweep results/water_targ_sweep_ALL_RESULTS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rchurchi\watertap\tutorials\flex_ro\sweep results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA57482E-4594-4EF8-92A5-118B128B7486}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A48E7D25-833C-4631-BC61-2F4BFB338A12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="0" windowWidth="9780" windowHeight="10170" xr2:uid="{811D88E6-5E04-4AC4-9B26-930D2EA2E3F2}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{811D88E6-5E04-4AC4-9B26-930D2EA2E3F2}"/>
   </bookViews>
   <sheets>
     <sheet name="Summer Cost Summary" sheetId="4" r:id="rId1"/>
@@ -624,24 +624,24 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B1DDFCB-CD48-4284-8222-18B5894FE623}">
   <dimension ref="A1:G21"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="9.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.453125" customWidth="1"/>
-    <col min="4" max="4" width="9.81640625" customWidth="1"/>
-    <col min="5" max="5" width="9.453125" customWidth="1"/>
-    <col min="6" max="6" width="10.36328125" customWidth="1"/>
+    <col min="2" max="2" width="9.23046875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.4609375" customWidth="1"/>
+    <col min="4" max="4" width="9.84375" customWidth="1"/>
+    <col min="5" max="5" width="9.4609375" customWidth="1"/>
+    <col min="6" max="6" width="10.3828125" customWidth="1"/>
     <col min="7" max="7" width="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="D1" s="6" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="6"/>
       <c r="F1" s="6"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="D2">
         <v>0</v>
       </c>
@@ -652,7 +652,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B3" t="s">
         <v>0</v>
       </c>
@@ -660,7 +660,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -674,7 +674,7 @@
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B5" s="3">
         <f>C5/$G$10</f>
         <v>1798.4286079070769</v>
@@ -685,7 +685,7 @@
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B6" s="3">
         <f>C6/$G$10</f>
         <v>2397.9615120043568</v>
@@ -695,22 +695,22 @@
       </c>
       <c r="D6" s="1"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
       <c r="D7" s="1"/>
       <c r="F7" s="1"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
       <c r="D8" s="1"/>
       <c r="F8" s="1"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
       <c r="D9" s="1"/>
       <c r="F9" s="1"/>
       <c r="G9" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B10">
         <v>8000</v>
       </c>
@@ -726,7 +726,7 @@
         <v>23.514972912500003</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B11">
         <v>9000</v>
       </c>
@@ -738,7 +738,7 @@
       </c>
       <c r="F11" s="1"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" hidden="1" x14ac:dyDescent="0.4">
       <c r="B12" s="3">
         <f>C12/$G$10</f>
         <v>9591.8460480174272</v>
@@ -749,7 +749,7 @@
       <c r="D12" s="1"/>
       <c r="F12" s="1"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B13">
         <v>10000</v>
       </c>
@@ -762,7 +762,7 @@
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B14">
         <v>11000</v>
       </c>
@@ -775,7 +775,7 @@
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B15">
         <v>12000</v>
       </c>
@@ -788,7 +788,7 @@
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
       <c r="B16">
         <v>13000</v>
       </c>
@@ -801,7 +801,7 @@
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B17">
         <v>14000</v>
       </c>
@@ -814,7 +814,7 @@
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B18">
         <v>15000</v>
       </c>
@@ -827,7 +827,7 @@
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
       <c r="B19">
         <v>16000</v>
       </c>
@@ -840,7 +840,7 @@
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
         <v>3</v>
       </c>
@@ -857,7 +857,7 @@
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
       <c r="C21">
         <f>C20*4/7</f>
         <v>225552</v>
@@ -868,30 +868,31 @@
     <mergeCell ref="D1:F1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E02D5E1-F801-4839-8C05-CA5C31CB2DFA}">
   <dimension ref="B1:H22"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="3" max="3" width="9.26953125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.453125" customWidth="1"/>
-    <col min="5" max="5" width="9.81640625" customWidth="1"/>
-    <col min="6" max="6" width="9.453125" customWidth="1"/>
-    <col min="7" max="7" width="10.36328125" customWidth="1"/>
+    <col min="3" max="3" width="9.23046875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.4609375" customWidth="1"/>
+    <col min="5" max="5" width="9.84375" customWidth="1"/>
+    <col min="6" max="6" width="9.4609375" customWidth="1"/>
+    <col min="7" max="7" width="10.3828125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="2:8" x14ac:dyDescent="0.4">
       <c r="E1" s="6" t="s">
         <v>2</v>
       </c>
       <c r="F1" s="6"/>
       <c r="G1" s="6"/>
     </row>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:8" x14ac:dyDescent="0.4">
       <c r="E2">
         <v>0</v>
       </c>
@@ -902,7 +903,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C3" t="s">
         <v>0</v>
       </c>
@@ -910,7 +911,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.4">
       <c r="B4" t="s">
         <v>4</v>
       </c>
@@ -926,7 +927,7 @@
         <v>16720.240035535448</v>
       </c>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C5">
         <v>1798</v>
       </c>
@@ -939,7 +940,7 @@
         <v>22368.52857086459</v>
       </c>
     </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C6">
         <v>2398</v>
       </c>
@@ -952,7 +953,7 @@
         <v>28772.571914996501</v>
       </c>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C7">
         <v>3000</v>
       </c>
@@ -961,7 +962,7 @@
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C8">
         <v>4000</v>
       </c>
@@ -974,7 +975,7 @@
       </c>
       <c r="G8" s="1"/>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C9">
         <v>5000</v>
       </c>
@@ -987,7 +988,7 @@
       </c>
       <c r="G9" s="1"/>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C10">
         <v>6000</v>
       </c>
@@ -1003,7 +1004,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C11">
         <v>7000</v>
       </c>
@@ -1016,7 +1017,7 @@
       </c>
       <c r="G11" s="1"/>
     </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C12">
         <v>8000</v>
       </c>
@@ -1035,7 +1036,7 @@
         <v>23.514972602724001</v>
       </c>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C13">
         <v>9000</v>
       </c>
@@ -1050,7 +1051,7 @@
       </c>
       <c r="G13" s="1"/>
     </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C14" s="3">
         <f>D14/H12</f>
         <v>9591.8461743762273</v>
@@ -1061,52 +1062,69 @@
       <c r="E14" s="1"/>
       <c r="G14" s="1"/>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C15">
         <v>10000</v>
       </c>
+      <c r="D15" s="3">
+        <f>C15*$H$12</f>
+        <v>235149.72602724002</v>
+      </c>
       <c r="E15">
         <v>93848</v>
       </c>
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:8" x14ac:dyDescent="0.4">
       <c r="C16">
         <v>11000</v>
       </c>
+      <c r="D16" s="3">
+        <f t="shared" ref="D16:D22" si="0">C16*$H$12</f>
+        <v>258664.698629964</v>
+      </c>
       <c r="E16" s="3">
         <v>102961.15922754805</v>
       </c>
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:7" x14ac:dyDescent="0.4">
       <c r="C17">
         <v>12000</v>
       </c>
+      <c r="D17" s="3">
+        <f t="shared" si="0"/>
+        <v>282179.67123268801</v>
+      </c>
       <c r="E17">
         <v>112554.99851567688</v>
       </c>
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
     </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:7" x14ac:dyDescent="0.4">
       <c r="C18">
         <v>13000</v>
       </c>
+      <c r="D18" s="3">
+        <f t="shared" si="0"/>
+        <v>305694.64383541199</v>
+      </c>
       <c r="E18" s="3">
         <v>121344.56621300505</v>
       </c>
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
     </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.4">
       <c r="C19">
         <v>14000</v>
       </c>
       <c r="D19" s="3">
-        <v>329240.017626649</v>
+        <f t="shared" si="0"/>
+        <v>329209.61643813603</v>
       </c>
       <c r="E19" s="3">
         <v>130424.39365381806</v>
@@ -1114,35 +1132,44 @@
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
     </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:7" x14ac:dyDescent="0.4">
       <c r="C20">
         <v>15000</v>
       </c>
+      <c r="D20" s="3">
+        <f t="shared" si="0"/>
+        <v>352724.58904086001</v>
+      </c>
       <c r="E20" s="3">
         <v>140645.20979357499</v>
       </c>
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
     </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:7" x14ac:dyDescent="0.4">
       <c r="C21">
         <v>16000</v>
       </c>
+      <c r="D21" s="3">
+        <f t="shared" si="0"/>
+        <v>376239.56164358399</v>
+      </c>
       <c r="E21" s="3">
         <v>149838.83143944858</v>
       </c>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
     </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:7" x14ac:dyDescent="0.4">
       <c r="B22" t="s">
         <v>3</v>
       </c>
       <c r="C22" s="3">
         <v>16785.730584030498</v>
       </c>
-      <c r="D22">
-        <v>394716</v>
+      <c r="D22" s="3">
+        <f t="shared" si="0"/>
+        <v>394715.99480018351</v>
       </c>
       <c r="E22" s="3">
         <v>158104.1957609462</v>
@@ -1155,34 +1182,35 @@
     <mergeCell ref="E1:G1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44889D92-5C1B-43B6-BE00-3D23C35CC93C}">
   <dimension ref="A1:Q39"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="8.7265625" customWidth="1"/>
-    <col min="2" max="3" width="11.81640625" customWidth="1"/>
-    <col min="4" max="4" width="22.26953125" customWidth="1"/>
-    <col min="5" max="5" width="28.81640625" customWidth="1"/>
-    <col min="6" max="6" width="26.90625" customWidth="1"/>
+    <col min="1" max="1" width="8.69140625" customWidth="1"/>
+    <col min="2" max="3" width="11.84375" customWidth="1"/>
+    <col min="4" max="4" width="22.23046875" customWidth="1"/>
+    <col min="5" max="5" width="28.84375" customWidth="1"/>
+    <col min="6" max="6" width="26.921875" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="20.08984375" customWidth="1"/>
-    <col min="9" max="9" width="21.54296875" customWidth="1"/>
-    <col min="10" max="10" width="18.453125" customWidth="1"/>
-    <col min="11" max="11" width="18.81640625" customWidth="1"/>
+    <col min="8" max="8" width="20.07421875" customWidth="1"/>
+    <col min="9" max="9" width="21.53515625" customWidth="1"/>
+    <col min="10" max="10" width="18.4609375" customWidth="1"/>
+    <col min="11" max="11" width="18.84375" customWidth="1"/>
     <col min="12" max="12" width="22" customWidth="1"/>
-    <col min="13" max="13" width="22.54296875" customWidth="1"/>
-    <col min="14" max="14" width="25.36328125" customWidth="1"/>
-    <col min="15" max="15" width="19.1796875" customWidth="1"/>
-    <col min="16" max="16" width="28.6328125" customWidth="1"/>
-    <col min="17" max="17" width="16.26953125" style="3" customWidth="1"/>
+    <col min="13" max="13" width="22.53515625" customWidth="1"/>
+    <col min="14" max="14" width="25.3828125" customWidth="1"/>
+    <col min="15" max="15" width="19.15234375" customWidth="1"/>
+    <col min="16" max="16" width="28.61328125" customWidth="1"/>
+    <col min="17" max="17" width="16.23046875" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
         <v>18</v>
       </c>
@@ -1235,7 +1263,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
         <v>19</v>
       </c>
@@ -1289,7 +1317,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -1343,7 +1371,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -1397,7 +1425,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -1451,7 +1479,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -1505,7 +1533,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -1556,7 +1584,7 @@
         <v>2.6406704469603199</v>
       </c>
     </row>
-    <row r="8" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -1607,7 +1635,7 @@
         <v>3.36954571208561</v>
       </c>
     </row>
-    <row r="9" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -1658,7 +1686,7 @@
         <v>4.8864727960722396</v>
       </c>
     </row>
-    <row r="10" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
         <v>21</v>
       </c>
@@ -1712,7 +1740,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -1763,7 +1791,7 @@
         <v>1.7211299327173799</v>
       </c>
     </row>
-    <row r="12" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -1814,7 +1842,7 @@
         <v>1.45968753918303</v>
       </c>
     </row>
-    <row r="13" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
         <v>19</v>
       </c>
@@ -1865,7 +1893,7 @@
         <v>1.2818199310829099</v>
       </c>
     </row>
-    <row r="14" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
         <v>19</v>
       </c>
@@ -1916,7 +1944,7 @@
         <v>1.15734642471583</v>
       </c>
     </row>
-    <row r="15" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
         <v>19</v>
       </c>
@@ -1967,7 +1995,7 @@
         <v>1.06438923423513</v>
       </c>
     </row>
-    <row r="16" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
         <v>19</v>
       </c>
@@ -2018,7 +2046,7 @@
         <v>0.99711288227329198</v>
       </c>
     </row>
-    <row r="17" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -2072,7 +2100,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
         <v>21</v>
       </c>
@@ -2126,7 +2154,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
         <v>21</v>
       </c>
@@ -2180,7 +2208,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -2234,7 +2262,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
         <v>19</v>
       </c>
@@ -2288,7 +2316,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
         <v>21</v>
       </c>
@@ -2342,7 +2370,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="23" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
         <v>21</v>
       </c>
@@ -2396,7 +2424,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="24" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
         <v>19</v>
       </c>
@@ -2450,7 +2478,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
         <v>21</v>
       </c>
@@ -2504,7 +2532,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
         <v>21</v>
       </c>
@@ -2558,7 +2586,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="27" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
         <v>21</v>
       </c>
@@ -2612,7 +2640,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
         <v>21</v>
       </c>
@@ -2666,7 +2694,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="29" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
         <v>21</v>
       </c>
@@ -2720,7 +2748,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="30" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
         <v>21</v>
       </c>
@@ -2774,7 +2802,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="31" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
         <v>21</v>
       </c>
@@ -2828,7 +2856,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="32" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
         <v>21</v>
       </c>
@@ -2882,7 +2910,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="33" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
         <v>21</v>
       </c>
@@ -2936,7 +2964,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="34" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
         <v>19</v>
       </c>
@@ -2990,7 +3018,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="35" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
         <v>19</v>
       </c>
@@ -3042,7 +3070,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
         <v>19</v>
       </c>
@@ -3096,7 +3124,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="37" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A37" t="s">
         <v>19</v>
       </c>
@@ -3150,7 +3178,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="38" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
         <v>19</v>
       </c>
@@ -3204,7 +3232,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="39" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
         <v>19</v>
       </c>

--- a/tutorials/flex_ro/sweep results/water_targ_sweep_ALL_RESULTS.xlsx
+++ b/tutorials/flex_ro/sweep results/water_targ_sweep_ALL_RESULTS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rchurchi\watertap\tutorials\flex_ro\sweep results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A48E7D25-833C-4631-BC61-2F4BFB338A12}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9220B6C1-4D79-4595-859C-361615C77A03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{811D88E6-5E04-4AC4-9B26-930D2EA2E3F2}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{811D88E6-5E04-4AC4-9B26-930D2EA2E3F2}"/>
   </bookViews>
   <sheets>
     <sheet name="Summer Cost Summary" sheetId="4" r:id="rId1"/>
@@ -623,25 +623,25 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B1DDFCB-CD48-4284-8222-18B5894FE623}">
-  <dimension ref="A1:G21"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:H21"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="9.23046875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.4609375" customWidth="1"/>
-    <col min="4" max="4" width="9.84375" customWidth="1"/>
-    <col min="5" max="5" width="9.4609375" customWidth="1"/>
-    <col min="6" max="6" width="10.3828125" customWidth="1"/>
+    <col min="2" max="2" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.453125" customWidth="1"/>
+    <col min="4" max="4" width="9.81640625" customWidth="1"/>
+    <col min="5" max="5" width="9.453125" customWidth="1"/>
+    <col min="6" max="6" width="10.36328125" customWidth="1"/>
     <col min="7" max="7" width="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="D1" s="6" t="s">
         <v>2</v>
       </c>
       <c r="E1" s="6"/>
       <c r="F1" s="6"/>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="D2">
         <v>0</v>
       </c>
@@ -652,7 +652,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>0</v>
       </c>
@@ -660,7 +660,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>4</v>
       </c>
@@ -674,7 +674,7 @@
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B5" s="3">
         <f>C5/$G$10</f>
         <v>1798.4286079070769</v>
@@ -685,7 +685,7 @@
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B6" s="3">
         <f>C6/$G$10</f>
         <v>2397.9615120043568</v>
@@ -695,22 +695,22 @@
       </c>
       <c r="D6" s="1"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="D7" s="1"/>
       <c r="F7" s="1"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="D8" s="1"/>
       <c r="F8" s="1"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="D9" s="1"/>
       <c r="F9" s="1"/>
       <c r="G9" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B10">
         <v>8000</v>
       </c>
@@ -726,7 +726,7 @@
         <v>23.514972912500003</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B11">
         <v>9000</v>
       </c>
@@ -738,7 +738,7 @@
       </c>
       <c r="F11" s="1"/>
     </row>
-    <row r="12" spans="1:7" hidden="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
       <c r="B12" s="3">
         <f>C12/$G$10</f>
         <v>9591.8460480174272</v>
@@ -749,7 +749,7 @@
       <c r="D12" s="1"/>
       <c r="F12" s="1"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B13">
         <v>10000</v>
       </c>
@@ -762,7 +762,7 @@
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B14">
         <v>11000</v>
       </c>
@@ -775,7 +775,7 @@
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B15">
         <v>12000</v>
       </c>
@@ -788,7 +788,7 @@
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="B16">
         <v>13000</v>
       </c>
@@ -801,7 +801,7 @@
       <c r="E16" s="1"/>
       <c r="F16" s="1"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B17">
         <v>14000</v>
       </c>
@@ -814,7 +814,7 @@
       <c r="E17" s="1"/>
       <c r="F17" s="1"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B18">
         <v>15000</v>
       </c>
@@ -827,7 +827,7 @@
       <c r="E18" s="1"/>
       <c r="F18" s="1"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B19">
         <v>16000</v>
       </c>
@@ -839,8 +839,16 @@
       </c>
       <c r="E19" s="1"/>
       <c r="F19" s="1"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G19">
+        <f>C19/1233.5</f>
+        <v>305.01788540237942</v>
+      </c>
+      <c r="H19">
+        <f>G19*13</f>
+        <v>3965.2325102309323</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>3</v>
       </c>
@@ -856,8 +864,16 @@
       </c>
       <c r="E20" s="1"/>
       <c r="F20" s="1"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
+      <c r="G20">
+        <f>C20/1233.5</f>
+        <v>319.99675719497367</v>
+      </c>
+      <c r="H20">
+        <f>G20*13</f>
+        <v>4159.9578435346575</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="C21">
         <f>C20*4/7</f>
         <v>225552</v>
@@ -876,23 +892,23 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E02D5E1-F801-4839-8C05-CA5C31CB2DFA}">
   <dimension ref="B1:H22"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="3" max="3" width="9.23046875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.4609375" customWidth="1"/>
-    <col min="5" max="5" width="9.84375" customWidth="1"/>
-    <col min="6" max="6" width="9.4609375" customWidth="1"/>
-    <col min="7" max="7" width="10.3828125" customWidth="1"/>
+    <col min="3" max="3" width="9.26953125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.453125" customWidth="1"/>
+    <col min="5" max="5" width="9.81640625" customWidth="1"/>
+    <col min="6" max="6" width="9.453125" customWidth="1"/>
+    <col min="7" max="7" width="10.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="1" spans="2:8" x14ac:dyDescent="0.35">
       <c r="E1" s="6" t="s">
         <v>2</v>
       </c>
       <c r="F1" s="6"/>
       <c r="G1" s="6"/>
     </row>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:8" x14ac:dyDescent="0.35">
       <c r="E2">
         <v>0</v>
       </c>
@@ -903,7 +919,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.35">
       <c r="C3" t="s">
         <v>0</v>
       </c>
@@ -911,7 +927,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
         <v>4</v>
       </c>
@@ -927,7 +943,7 @@
         <v>16720.240035535448</v>
       </c>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.35">
       <c r="C5">
         <v>1798</v>
       </c>
@@ -940,7 +956,7 @@
         <v>22368.52857086459</v>
       </c>
     </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="6" spans="2:8" x14ac:dyDescent="0.35">
       <c r="C6">
         <v>2398</v>
       </c>
@@ -953,7 +969,7 @@
         <v>28772.571914996501</v>
       </c>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.35">
       <c r="C7">
         <v>3000</v>
       </c>
@@ -962,7 +978,7 @@
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.35">
       <c r="C8">
         <v>4000</v>
       </c>
@@ -975,7 +991,7 @@
       </c>
       <c r="G8" s="1"/>
     </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="9" spans="2:8" x14ac:dyDescent="0.35">
       <c r="C9">
         <v>5000</v>
       </c>
@@ -988,7 +1004,7 @@
       </c>
       <c r="G9" s="1"/>
     </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="10" spans="2:8" x14ac:dyDescent="0.35">
       <c r="C10">
         <v>6000</v>
       </c>
@@ -1004,7 +1020,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="11" spans="2:8" x14ac:dyDescent="0.35">
       <c r="C11">
         <v>7000</v>
       </c>
@@ -1017,7 +1033,7 @@
       </c>
       <c r="G11" s="1"/>
     </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="12" spans="2:8" x14ac:dyDescent="0.35">
       <c r="C12">
         <v>8000</v>
       </c>
@@ -1036,7 +1052,7 @@
         <v>23.514972602724001</v>
       </c>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="13" spans="2:8" x14ac:dyDescent="0.35">
       <c r="C13">
         <v>9000</v>
       </c>
@@ -1051,7 +1067,7 @@
       </c>
       <c r="G13" s="1"/>
     </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="14" spans="2:8" x14ac:dyDescent="0.35">
       <c r="C14" s="3">
         <f>D14/H12</f>
         <v>9591.8461743762273</v>
@@ -1062,7 +1078,7 @@
       <c r="E14" s="1"/>
       <c r="G14" s="1"/>
     </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="15" spans="2:8" x14ac:dyDescent="0.35">
       <c r="C15">
         <v>10000</v>
       </c>
@@ -1076,7 +1092,7 @@
       <c r="F15" s="1"/>
       <c r="G15" s="1"/>
     </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.4">
+    <row r="16" spans="2:8" x14ac:dyDescent="0.35">
       <c r="C16">
         <v>11000</v>
       </c>
@@ -1090,7 +1106,7 @@
       <c r="F16" s="1"/>
       <c r="G16" s="1"/>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="17" spans="2:7" x14ac:dyDescent="0.35">
       <c r="C17">
         <v>12000</v>
       </c>
@@ -1104,7 +1120,7 @@
       <c r="F17" s="1"/>
       <c r="G17" s="1"/>
     </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="18" spans="2:7" x14ac:dyDescent="0.35">
       <c r="C18">
         <v>13000</v>
       </c>
@@ -1118,7 +1134,7 @@
       <c r="F18" s="1"/>
       <c r="G18" s="1"/>
     </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="19" spans="2:7" x14ac:dyDescent="0.35">
       <c r="C19">
         <v>14000</v>
       </c>
@@ -1132,7 +1148,7 @@
       <c r="F19" s="1"/>
       <c r="G19" s="1"/>
     </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="20" spans="2:7" x14ac:dyDescent="0.35">
       <c r="C20">
         <v>15000</v>
       </c>
@@ -1146,7 +1162,7 @@
       <c r="F20" s="1"/>
       <c r="G20" s="1"/>
     </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="21" spans="2:7" x14ac:dyDescent="0.35">
       <c r="C21">
         <v>16000</v>
       </c>
@@ -1160,7 +1176,7 @@
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
     </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.4">
+    <row r="22" spans="2:7" x14ac:dyDescent="0.35">
       <c r="B22" t="s">
         <v>3</v>
       </c>
@@ -1190,27 +1206,27 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44889D92-5C1B-43B6-BE00-3D23C35CC93C}">
   <dimension ref="A1:Q39"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.69140625" customWidth="1"/>
-    <col min="2" max="3" width="11.84375" customWidth="1"/>
-    <col min="4" max="4" width="22.23046875" customWidth="1"/>
-    <col min="5" max="5" width="28.84375" customWidth="1"/>
-    <col min="6" max="6" width="26.921875" customWidth="1"/>
+    <col min="1" max="1" width="8.7265625" customWidth="1"/>
+    <col min="2" max="3" width="11.81640625" customWidth="1"/>
+    <col min="4" max="4" width="22.26953125" customWidth="1"/>
+    <col min="5" max="5" width="28.81640625" customWidth="1"/>
+    <col min="6" max="6" width="26.90625" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="20.07421875" customWidth="1"/>
-    <col min="9" max="9" width="21.53515625" customWidth="1"/>
-    <col min="10" max="10" width="18.4609375" customWidth="1"/>
-    <col min="11" max="11" width="18.84375" customWidth="1"/>
+    <col min="8" max="8" width="20.08984375" customWidth="1"/>
+    <col min="9" max="9" width="21.54296875" customWidth="1"/>
+    <col min="10" max="10" width="18.453125" customWidth="1"/>
+    <col min="11" max="11" width="18.81640625" customWidth="1"/>
     <col min="12" max="12" width="22" customWidth="1"/>
-    <col min="13" max="13" width="22.53515625" customWidth="1"/>
-    <col min="14" max="14" width="25.3828125" customWidth="1"/>
-    <col min="15" max="15" width="19.15234375" customWidth="1"/>
-    <col min="16" max="16" width="28.61328125" customWidth="1"/>
-    <col min="17" max="17" width="16.23046875" style="3" customWidth="1"/>
+    <col min="13" max="13" width="22.54296875" customWidth="1"/>
+    <col min="14" max="14" width="25.36328125" customWidth="1"/>
+    <col min="15" max="15" width="19.1796875" customWidth="1"/>
+    <col min="16" max="16" width="28.6328125" customWidth="1"/>
+    <col min="17" max="17" width="16.26953125" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>18</v>
       </c>
@@ -1263,7 +1279,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>19</v>
       </c>
@@ -1317,7 +1333,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>21</v>
       </c>
@@ -1371,7 +1387,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -1425,7 +1441,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>21</v>
       </c>
@@ -1479,7 +1495,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>21</v>
       </c>
@@ -1533,7 +1549,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>19</v>
       </c>
@@ -1584,7 +1600,7 @@
         <v>2.6406704469603199</v>
       </c>
     </row>
-    <row r="8" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>19</v>
       </c>
@@ -1635,7 +1651,7 @@
         <v>3.36954571208561</v>
       </c>
     </row>
-    <row r="9" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>19</v>
       </c>
@@ -1686,7 +1702,7 @@
         <v>4.8864727960722396</v>
       </c>
     </row>
-    <row r="10" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>21</v>
       </c>
@@ -1740,7 +1756,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>19</v>
       </c>
@@ -1791,7 +1807,7 @@
         <v>1.7211299327173799</v>
       </c>
     </row>
-    <row r="12" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>19</v>
       </c>
@@ -1842,7 +1858,7 @@
         <v>1.45968753918303</v>
       </c>
     </row>
-    <row r="13" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>19</v>
       </c>
@@ -1893,7 +1909,7 @@
         <v>1.2818199310829099</v>
       </c>
     </row>
-    <row r="14" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>19</v>
       </c>
@@ -1944,7 +1960,7 @@
         <v>1.15734642471583</v>
       </c>
     </row>
-    <row r="15" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>19</v>
       </c>
@@ -1995,7 +2011,7 @@
         <v>1.06438923423513</v>
       </c>
     </row>
-    <row r="16" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>19</v>
       </c>
@@ -2046,7 +2062,7 @@
         <v>0.99711288227329198</v>
       </c>
     </row>
-    <row r="17" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>21</v>
       </c>
@@ -2100,7 +2116,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>21</v>
       </c>
@@ -2154,7 +2170,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>21</v>
       </c>
@@ -2208,7 +2224,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="20" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>19</v>
       </c>
@@ -2262,7 +2278,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="21" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>19</v>
       </c>
@@ -2316,7 +2332,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="22" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>21</v>
       </c>
@@ -2370,7 +2386,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="23" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>21</v>
       </c>
@@ -2424,7 +2440,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="24" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>19</v>
       </c>
@@ -2478,7 +2494,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="25" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>21</v>
       </c>
@@ -2532,7 +2548,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>21</v>
       </c>
@@ -2586,7 +2602,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="27" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>21</v>
       </c>
@@ -2640,7 +2656,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>21</v>
       </c>
@@ -2694,7 +2710,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="29" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>21</v>
       </c>
@@ -2748,7 +2764,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="30" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>21</v>
       </c>
@@ -2802,7 +2818,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="31" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>21</v>
       </c>
@@ -2856,7 +2872,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="32" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>21</v>
       </c>
@@ -2910,7 +2926,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="33" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>21</v>
       </c>
@@ -2964,7 +2980,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="34" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>19</v>
       </c>
@@ -3018,7 +3034,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="35" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>19</v>
       </c>
@@ -3070,7 +3086,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="36" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>19</v>
       </c>
@@ -3124,7 +3140,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="37" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>19</v>
       </c>
@@ -3178,7 +3194,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="38" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>19</v>
       </c>
@@ -3232,7 +3248,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="39" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>19</v>
       </c>

--- a/tutorials/flex_ro/sweep results/water_targ_sweep_ALL_RESULTS.xlsx
+++ b/tutorials/flex_ro/sweep results/water_targ_sweep_ALL_RESULTS.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rchurchi\watertap\tutorials\flex_ro\sweep results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9220B6C1-4D79-4595-859C-361615C77A03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2891B258-AE50-4BF5-ACD6-69708635C66E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{811D88E6-5E04-4AC4-9B26-930D2EA2E3F2}"/>
+    <workbookView xWindow="-80" yWindow="-80" windowWidth="19360" windowHeight="10240" xr2:uid="{811D88E6-5E04-4AC4-9B26-930D2EA2E3F2}"/>
   </bookViews>
   <sheets>
     <sheet name="Summer Cost Summary" sheetId="4" r:id="rId1"/>
@@ -44,7 +44,7 @@
     <author>tc={C6F4AE83-B49D-43EA-8F80-7B60FB4267DD}</author>
   </authors>
   <commentList>
-    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{7A97C2A1-F701-44DC-ACFB-FB00CE8362D6}">
+    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{7A97C2A1-F701-44DC-ACFB-FB00CE8362D6}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -71,7 +71,7 @@
     <author>tc={2CD69954-9FBF-4F0C-A085-7745F169BA9F}</author>
   </authors>
   <commentList>
-    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{4E18937C-0B14-4E86-B599-4BF7BA80B225}">
+    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{4E18937C-0B14-4E86-B599-4BF7BA80B225}">
       <text>
         <t>[Threaded comment]
 Your version of Excel allows you to read this threaded comment; however, any edits to it will get removed if the file is opened in a newer version of Excel. Learn more: https://go.microsoft.com/fwlink/?linkid=870924
@@ -92,12 +92,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="29">
   <si>
     <t>Annual AF</t>
-  </si>
-  <si>
-    <t>Weekly Water</t>
   </si>
   <si>
     <t># of Rainy Days</t>
@@ -174,11 +171,24 @@
   <si>
     <t>N</t>
   </si>
+  <si>
+    <t>Weekly Water (m3)</t>
+  </si>
+  <si>
+    <t>Weekly Water (AF)</t>
+  </si>
+  <si>
+    <t>Average Water (MGD)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0"/>
+  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -233,7 +243,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -243,6 +253,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -283,6 +296,2030 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="0"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-7.5927966324985066E-2"/>
+                  <c:y val="-2.317074948964715E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Summer Cost Summary'!$D$10:$D$18</c:f>
+              <c:numCache>
+                <c:formatCode>0.0</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>152.50894471017432</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>171.57257843206241</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>190.63617837648562</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>209.69979643291447</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>228.76341405154196</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>247.82703188943333</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>266.89064969598701</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>286.02286511020429</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Summer Cost Summary'!$F$10:$F$20</c:f>
+              <c:numCache>
+                <c:formatCode>"$"#,##0</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>80541.55863</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>90280.635276184097</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>99135.784106883366</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>108042.46335199999</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>117856.65704778227</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>126980.73146875472</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>135947.17095224367</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>146231.12922675692</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>159412.81974307698</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>171053.54809522501</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-1A53-419D-BC84-B0A81357CD5A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="772037264"/>
+        <c:axId val="772226720"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="772037264"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0.0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="772226720"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="772226720"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="&quot;$&quot;#,##0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="772037264"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="25400" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="0"/>
+          </c:trendline>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="0"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-6.0829632159531362E-2"/>
+                  <c:y val="-3.7005062779517074E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="en-US"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>'Winter Cost Summary'!$E$12:$E$22</c:f>
+              <c:numCache>
+                <c:formatCode>0</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>152.50894270108796</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>171.57256053883827</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>190.63617837635996</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>209.69979621399594</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>228.76341405163194</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>247.82703188926791</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>266.89064972690397</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>285.95426756453992</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>305.01788540217592</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>319.9967529794759</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>'Winter Cost Summary'!$G$12:$G$22</c:f>
+              <c:numCache>
+                <c:formatCode>"$"#,##0</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>75507</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>85155.50909649636</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>93848</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>102961.15922754805</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>112554.99851567688</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>121344.56621300505</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>130424.39365381806</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>140645.20979357499</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>149838.83143944858</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>158104.1957609462</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-1EA7-46BE-9DD7-86E6C38212C6}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="821892088"/>
+        <c:axId val="821893168"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="821892088"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="821893168"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="821893168"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="&quot;$&quot;#,##0" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="821892088"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>999444</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>161244</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>331333</xdr:colOff>
+      <xdr:row>38</xdr:row>
+      <xdr:rowOff>8844</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FCF66BEB-3508-F947-4A3A-D7F0962EE260}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>606879</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>143555</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1D7AEB8B-231B-882B-EB5C-25828C1FF1C2}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
@@ -601,7 +2638,7 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="D1" dT="2026-08-21T19:08:40.15" personId="{D208FEB8-F7DA-4D83-AAE5-2EEFF5739FC7}" id="{7A97C2A1-F701-44DC-ACFB-FB00CE8362D6}">
+  <threadedComment ref="F1" dT="2026-08-21T19:08:40.15" personId="{D208FEB8-F7DA-4D83-AAE5-2EEFF5739FC7}" id="{7A97C2A1-F701-44DC-ACFB-FB00CE8362D6}">
     <text>This is fine for winter, but for the summer, this would highly bias the results towards the weekend.</text>
   </threadedComment>
   <threadedComment ref="A4" dT="2026-08-21T19:09:12.49" personId="{D208FEB8-F7DA-4D83-AAE5-2EEFF5739FC7}" id="{C6F4AE83-B49D-43EA-8F80-7B60FB4267DD}">
@@ -612,7 +2649,7 @@
 
 <file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <threadedComment ref="E1" dT="2026-08-21T19:08:40.15" personId="{D208FEB8-F7DA-4D83-AAE5-2EEFF5739FC7}" id="{4E18937C-0B14-4E86-B599-4BF7BA80B225}">
+  <threadedComment ref="G1" dT="2026-08-21T19:08:40.15" personId="{D208FEB8-F7DA-4D83-AAE5-2EEFF5739FC7}" id="{4E18937C-0B14-4E86-B599-4BF7BA80B225}">
     <text>This is fine for winter, but for the summer, this would highly bias the results towards the weekend.</text>
   </threadedComment>
   <threadedComment ref="B4" dT="2026-08-21T19:09:12.49" personId="{D208FEB8-F7DA-4D83-AAE5-2EEFF5739FC7}" id="{2CD69954-9FBF-4F0C-A085-7745F169BA9F}">
@@ -623,257 +2660,385 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B1DDFCB-CD48-4284-8222-18B5894FE623}">
-  <dimension ref="A1:H21"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:J21"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="2" max="2" width="9.26953125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.453125" customWidth="1"/>
-    <col min="4" max="4" width="9.81640625" customWidth="1"/>
-    <col min="5" max="5" width="9.453125" customWidth="1"/>
-    <col min="6" max="6" width="10.36328125" customWidth="1"/>
-    <col min="7" max="7" width="18" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.23046875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.61328125" customWidth="1"/>
+    <col min="4" max="4" width="17.07421875" customWidth="1"/>
+    <col min="5" max="5" width="19.15234375" customWidth="1"/>
+    <col min="6" max="6" width="9.84375" customWidth="1"/>
+    <col min="7" max="7" width="9.4609375" customWidth="1"/>
+    <col min="8" max="8" width="10.3828125" customWidth="1"/>
+    <col min="9" max="9" width="18" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="D1" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="D2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="F1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.4">
+      <c r="F2">
         <v>0</v>
       </c>
-      <c r="E2">
+      <c r="G2">
         <v>3</v>
       </c>
-      <c r="F2">
+      <c r="H2">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.4">
       <c r="B3" t="s">
         <v>0</v>
       </c>
       <c r="C3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+        <v>26</v>
+      </c>
+      <c r="D3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4" s="3">
-        <f>C4/$G$10</f>
+        <f>C4/$I$10</f>
         <v>1190.7306933411717</v>
       </c>
       <c r="C4">
         <v>28000</v>
       </c>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.4">
       <c r="B5" s="3">
-        <f>C5/$G$10</f>
+        <f>C5/$I$10</f>
         <v>1798.4286079070769</v>
       </c>
       <c r="C5">
         <v>42290</v>
       </c>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.4">
       <c r="B6" s="3">
-        <f>C6/$G$10</f>
+        <f>C6/$I$10</f>
         <v>2397.9615120043568</v>
       </c>
       <c r="C6">
         <v>56388</v>
       </c>
-      <c r="D6" s="1"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="D7" s="1"/>
+      <c r="F6" s="1"/>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.4">
       <c r="F7" s="1"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="D8" s="1"/>
+      <c r="H7" s="1"/>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.4">
       <c r="F8" s="1"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="D9" s="1"/>
+      <c r="H8" s="1"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.4">
       <c r="F9" s="1"/>
-      <c r="G9" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H9" s="1"/>
+      <c r="I9" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.4">
       <c r="B10">
         <v>8000</v>
       </c>
       <c r="C10" s="3">
         <v>188119.78330000001</v>
       </c>
-      <c r="D10" s="3">
+      <c r="D10" s="7">
+        <f>C10/1233.5</f>
+        <v>152.50894471017432</v>
+      </c>
+      <c r="E10" s="7">
+        <f>C10*264.2/10^6/7</f>
+        <v>7.1001781068371423</v>
+      </c>
+      <c r="F10" s="8">
         <v>80541.55863</v>
       </c>
-      <c r="F10" s="1"/>
-      <c r="G10">
+      <c r="H10" s="1"/>
+      <c r="I10">
         <f>C10/B10</f>
         <v>23.514972912500003</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.4">
       <c r="B11">
         <v>9000</v>
       </c>
       <c r="C11" s="3">
         <v>211634.775495949</v>
       </c>
-      <c r="D11" s="3">
+      <c r="D11" s="7">
+        <f t="shared" ref="D11:D20" si="0">C11/1233.5</f>
+        <v>171.57257843206241</v>
+      </c>
+      <c r="E11" s="7">
+        <f t="shared" ref="E11:E20" si="1">C11*264.2/10^6/7</f>
+        <v>7.987701098004246</v>
+      </c>
+      <c r="F11" s="8">
         <v>90280.635276184097</v>
       </c>
-      <c r="F11" s="1"/>
-    </row>
-    <row r="12" spans="1:7" hidden="1" x14ac:dyDescent="0.35">
+      <c r="H11" s="1"/>
+      <c r="I11">
+        <f t="shared" ref="I11:I18" si="2">C11/1233.5</f>
+        <v>171.57257843206241</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" hidden="1" x14ac:dyDescent="0.4">
       <c r="B12" s="3">
-        <f>C12/$G$10</f>
+        <f>C12/$I$10</f>
         <v>9591.8460480174272</v>
       </c>
       <c r="C12">
         <v>225552</v>
       </c>
-      <c r="D12" s="1"/>
-      <c r="F12" s="1"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="D12" s="7">
+        <f t="shared" si="0"/>
+        <v>182.85528982569923</v>
+      </c>
+      <c r="E12" s="7">
+        <f t="shared" si="1"/>
+        <v>8.5129769142857139</v>
+      </c>
+      <c r="F12" s="9"/>
+      <c r="H12" s="1"/>
+      <c r="I12">
+        <f t="shared" si="2"/>
+        <v>182.85528982569923</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.4">
       <c r="B13">
         <v>10000</v>
       </c>
       <c r="C13" s="4">
         <v>235149.72602739499</v>
       </c>
-      <c r="D13" s="3">
+      <c r="D13" s="7">
+        <f t="shared" si="0"/>
+        <v>190.63617837648562</v>
+      </c>
+      <c r="E13" s="7">
+        <f t="shared" si="1"/>
+        <v>8.8752225166339649</v>
+      </c>
+      <c r="F13" s="8">
         <v>99135.784106883366</v>
       </c>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13">
+        <f t="shared" si="2"/>
+        <v>190.63617837648562</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.4">
       <c r="B14">
         <v>11000</v>
       </c>
       <c r="C14" s="3">
         <v>258664.69889999999</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="7">
+        <f t="shared" si="0"/>
+        <v>209.69979643291447</v>
+      </c>
+      <c r="E14" s="7">
+        <f t="shared" si="1"/>
+        <v>9.7627447784828565</v>
+      </c>
+      <c r="F14" s="8">
         <v>108042.46335199999</v>
       </c>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14">
+        <f t="shared" si="2"/>
+        <v>209.69979643291447</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.4">
       <c r="B15">
         <v>12000</v>
       </c>
       <c r="C15" s="3">
         <v>282179.67123257701</v>
       </c>
-      <c r="D15" s="3">
+      <c r="D15" s="7">
+        <f t="shared" si="0"/>
+        <v>228.76341405154196</v>
+      </c>
+      <c r="E15" s="7">
+        <f t="shared" si="1"/>
+        <v>10.650267019949549</v>
+      </c>
+      <c r="F15" s="8">
         <v>117856.65704778227</v>
       </c>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15">
+        <f t="shared" si="2"/>
+        <v>228.76341405154196</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.4">
       <c r="B16">
         <v>13000</v>
       </c>
       <c r="C16" s="3">
         <v>305694.64383561601</v>
       </c>
-      <c r="D16" s="3">
+      <c r="D16" s="7">
+        <f t="shared" si="0"/>
+        <v>247.82703188943333</v>
+      </c>
+      <c r="E16" s="7">
+        <f t="shared" si="1"/>
+        <v>11.53778927162425</v>
+      </c>
+      <c r="F16" s="8">
         <v>126980.73146875472</v>
       </c>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="G16" s="1"/>
+      <c r="H16" s="1"/>
+      <c r="I16">
+        <f t="shared" si="2"/>
+        <v>247.82703188943333</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.4">
       <c r="B17">
         <v>14000</v>
       </c>
       <c r="C17" s="3">
         <v>329209.6164</v>
       </c>
-      <c r="D17" s="3">
+      <c r="D17" s="7">
+        <f t="shared" si="0"/>
+        <v>266.89064969598701</v>
+      </c>
+      <c r="E17" s="7">
+        <f t="shared" si="1"/>
+        <v>12.425311521839999</v>
+      </c>
+      <c r="F17" s="8">
         <v>135947.17095224367</v>
       </c>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="G17" s="1"/>
+      <c r="H17" s="1"/>
+      <c r="I17">
+        <f t="shared" si="2"/>
+        <v>266.89064969598701</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.4">
       <c r="B18">
         <v>15000</v>
       </c>
       <c r="C18" s="3">
         <v>352809.20411343698</v>
       </c>
-      <c r="D18" s="3">
+      <c r="D18" s="7">
+        <f t="shared" si="0"/>
+        <v>286.02286511020429</v>
+      </c>
+      <c r="E18" s="7">
+        <f t="shared" si="1"/>
+        <v>13.316027389538577</v>
+      </c>
+      <c r="F18" s="8">
         <v>146231.12922675692</v>
       </c>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="G18" s="1"/>
+      <c r="H18" s="1"/>
+      <c r="I18">
+        <f t="shared" si="2"/>
+        <v>286.02286511020429</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.4">
       <c r="B19">
         <v>16000</v>
       </c>
       <c r="C19" s="3">
         <v>376239.56164383498</v>
       </c>
-      <c r="D19" s="3">
+      <c r="D19" s="7">
+        <f t="shared" si="0"/>
+        <v>305.01788540237942</v>
+      </c>
+      <c r="E19" s="7">
+        <f t="shared" si="1"/>
+        <v>14.200356026614458</v>
+      </c>
+      <c r="F19" s="8">
         <v>159412.81974307698</v>
       </c>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19">
+      <c r="G19" s="1"/>
+      <c r="H19" s="1"/>
+      <c r="I19">
         <f>C19/1233.5</f>
         <v>305.01788540237942</v>
       </c>
-      <c r="H19">
-        <f>G19*13</f>
+      <c r="J19">
+        <f>I19*13</f>
         <v>3965.2325102309323</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B20" s="3">
-        <f>C20/$G$10</f>
+        <f>C20/$I$10</f>
         <v>16785.730584030498</v>
       </c>
       <c r="C20" s="3">
         <v>394716</v>
       </c>
-      <c r="D20" s="3">
+      <c r="D20" s="7">
+        <f t="shared" si="0"/>
+        <v>319.99675719497367</v>
+      </c>
+      <c r="E20" s="7">
+        <f t="shared" si="1"/>
+        <v>14.897709599999999</v>
+      </c>
+      <c r="F20" s="8">
         <v>171053.54809522501</v>
       </c>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-      <c r="G20">
+      <c r="G20" s="1"/>
+      <c r="H20" s="1"/>
+      <c r="I20">
         <f>C20/1233.5</f>
         <v>319.99675719497367</v>
       </c>
-      <c r="H20">
-        <f>G20*13</f>
+      <c r="J20">
+        <f>I20*13</f>
         <v>4159.9578435346575</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.4">
       <c r="C21">
         <f>C20*4/7</f>
         <v>225552</v>
@@ -881,55 +3046,64 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="D1:F1"/>
+    <mergeCell ref="F1:H1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2E02D5E1-F801-4839-8C05-CA5C31CB2DFA}">
-  <dimension ref="B1:H22"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="B1:J22"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="3" max="3" width="9.26953125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="13.453125" customWidth="1"/>
-    <col min="5" max="5" width="9.81640625" customWidth="1"/>
-    <col min="6" max="6" width="9.453125" customWidth="1"/>
-    <col min="7" max="7" width="10.36328125" customWidth="1"/>
+    <col min="3" max="3" width="9.23046875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.4609375" customWidth="1"/>
+    <col min="5" max="5" width="18.3046875" customWidth="1"/>
+    <col min="6" max="6" width="17" customWidth="1"/>
+    <col min="7" max="7" width="9.84375" customWidth="1"/>
+    <col min="8" max="8" width="9.4609375" customWidth="1"/>
+    <col min="9" max="9" width="10.3828125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="E1" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-    </row>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="E2">
+    <row r="1" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="G1" s="6" t="s">
+        <v>1</v>
+      </c>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+    </row>
+    <row r="2" spans="2:10" x14ac:dyDescent="0.4">
+      <c r="G2">
         <v>0</v>
       </c>
-      <c r="F2">
+      <c r="H2">
         <v>3</v>
       </c>
-      <c r="G2">
+      <c r="I2">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.4">
       <c r="C3" t="s">
         <v>0</v>
       </c>
       <c r="D3" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="2:8" x14ac:dyDescent="0.35">
+        <v>26</v>
+      </c>
+      <c r="E3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.4">
       <c r="B4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C4">
         <v>1191</v>
@@ -937,122 +3111,146 @@
       <c r="D4" s="3">
         <v>28006.332369864798</v>
       </c>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="3">
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="3">
         <v>16720.240035535448</v>
       </c>
     </row>
-    <row r="5" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.4">
       <c r="C5">
         <v>1798</v>
       </c>
       <c r="D5" s="3">
         <v>42292.226399718798</v>
       </c>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="3">
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="3">
         <v>22368.52857086459</v>
       </c>
     </row>
-    <row r="6" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.4">
       <c r="C6">
         <v>2398</v>
       </c>
       <c r="D6" s="3">
         <v>56388.904300408598</v>
       </c>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="3">
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="3">
         <v>28772.571914996501</v>
       </c>
     </row>
-    <row r="7" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.4">
       <c r="C7">
         <v>3000</v>
       </c>
       <c r="D7" s="3"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
       <c r="G7" s="1"/>
-    </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.4">
       <c r="C8">
         <v>4000</v>
       </c>
       <c r="D8" s="3">
         <v>94059.890410960099</v>
       </c>
-      <c r="E8" s="1"/>
-      <c r="F8" s="3">
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="3">
         <v>41752.231305558547</v>
       </c>
-      <c r="G8" s="1"/>
-    </row>
-    <row r="9" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="I8" s="1"/>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.4">
       <c r="C9">
         <v>5000</v>
       </c>
       <c r="D9" s="3">
         <v>117574.86301369801</v>
       </c>
-      <c r="E9" s="1"/>
-      <c r="F9" s="3">
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="3">
         <v>51495.778789739757</v>
       </c>
-      <c r="G9" s="1"/>
-    </row>
-    <row r="10" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="I9" s="1"/>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.4">
       <c r="C10">
         <v>6000</v>
       </c>
       <c r="D10" s="3">
         <v>141089.835616439</v>
       </c>
-      <c r="E10" s="1"/>
-      <c r="F10" s="3">
+      <c r="E10" s="3"/>
+      <c r="F10" s="3"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="3">
         <v>60724.979693855727</v>
       </c>
-      <c r="G10" s="1"/>
-      <c r="H10" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="I10" s="1"/>
+      <c r="J10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.4">
       <c r="C11">
         <v>7000</v>
       </c>
       <c r="D11" s="3">
         <v>164604.808219178</v>
       </c>
-      <c r="E11" s="1"/>
-      <c r="F11" s="3">
+      <c r="E11" s="3"/>
+      <c r="F11" s="3"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="3">
         <v>70388.430895292957</v>
       </c>
-      <c r="G11" s="1"/>
-    </row>
-    <row r="12" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="I11" s="1"/>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.4">
       <c r="C12">
         <v>8000</v>
       </c>
       <c r="D12" s="3">
         <v>188119.780821792</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="3">
+        <f>D12/1233.5</f>
+        <v>152.50894270108796</v>
+      </c>
+      <c r="F12" s="7">
+        <f>D12*264.2/10^6/7</f>
+        <v>7.1001780133024921</v>
+      </c>
+      <c r="G12" s="8">
         <v>75507</v>
       </c>
-      <c r="F12" s="3">
+      <c r="H12" s="3">
         <v>80116.314065181752</v>
       </c>
-      <c r="G12" s="1"/>
-      <c r="H12">
+      <c r="I12" s="1"/>
+      <c r="J12">
         <f>D12/C12</f>
         <v>23.514972602724001</v>
       </c>
     </row>
-    <row r="13" spans="2:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:10" x14ac:dyDescent="0.4">
       <c r="C13">
         <v>9000</v>
       </c>
@@ -1060,228 +3258,309 @@
         <v>211634.75342465701</v>
       </c>
       <c r="E13" s="3">
+        <f t="shared" ref="E13:E22" si="0">D13/1233.5</f>
+        <v>171.57256053883827</v>
+      </c>
+      <c r="F13" s="7">
+        <f t="shared" ref="F13:F22" si="1">D13*264.2/10^6/7</f>
+        <v>7.9877002649706261</v>
+      </c>
+      <c r="G13" s="8">
         <v>85155.50909649636</v>
       </c>
-      <c r="F13" s="3">
+      <c r="H13" s="3">
         <v>90891.797768890829</v>
       </c>
-      <c r="G13" s="1"/>
-    </row>
-    <row r="14" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="I13" s="1"/>
+    </row>
+    <row r="14" spans="2:10" hidden="1" x14ac:dyDescent="0.4">
       <c r="C14" s="3">
-        <f>D14/H12</f>
+        <f>D14/J12</f>
         <v>9591.8461743762273</v>
       </c>
       <c r="D14">
         <v>225552</v>
       </c>
-      <c r="E14" s="1"/>
-      <c r="G14" s="1"/>
-    </row>
-    <row r="15" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="E14" s="3">
+        <f t="shared" si="0"/>
+        <v>182.85528982569923</v>
+      </c>
+      <c r="F14" s="7">
+        <f t="shared" si="1"/>
+        <v>8.5129769142857139</v>
+      </c>
+      <c r="G14" s="9"/>
+      <c r="I14" s="1"/>
+    </row>
+    <row r="15" spans="2:10" x14ac:dyDescent="0.4">
       <c r="C15">
         <v>10000</v>
       </c>
       <c r="D15" s="3">
-        <f>C15*$H$12</f>
+        <f>C15*$J$12</f>
         <v>235149.72602724002</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="3">
+        <f t="shared" si="0"/>
+        <v>190.63617837635996</v>
+      </c>
+      <c r="F15" s="7">
+        <f t="shared" si="1"/>
+        <v>8.8752225166281153</v>
+      </c>
+      <c r="G15" s="8">
         <v>93848</v>
       </c>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-    </row>
-    <row r="16" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.4">
       <c r="C16">
         <v>11000</v>
       </c>
       <c r="D16" s="3">
-        <f t="shared" ref="D16:D22" si="0">C16*$H$12</f>
+        <f t="shared" ref="D16:D22" si="2">C16*$J$12</f>
         <v>258664.698629964</v>
       </c>
       <c r="E16" s="3">
+        <f t="shared" si="0"/>
+        <v>209.69979621399594</v>
+      </c>
+      <c r="F16" s="7">
+        <f t="shared" si="1"/>
+        <v>9.7627447682909274</v>
+      </c>
+      <c r="G16" s="8">
         <v>102961.15922754805</v>
       </c>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-    </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="H16" s="1"/>
+      <c r="I16" s="1"/>
+    </row>
+    <row r="17" spans="2:9" x14ac:dyDescent="0.4">
       <c r="C17">
         <v>12000</v>
       </c>
       <c r="D17" s="3">
+        <f t="shared" si="2"/>
+        <v>282179.67123268801</v>
+      </c>
+      <c r="E17" s="3">
         <f t="shared" si="0"/>
-        <v>282179.67123268801</v>
-      </c>
-      <c r="E17">
+        <v>228.76341405163194</v>
+      </c>
+      <c r="F17" s="7">
+        <f t="shared" si="1"/>
+        <v>10.650267019953739</v>
+      </c>
+      <c r="G17" s="8">
         <v>112554.99851567688</v>
       </c>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-    </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="H17" s="1"/>
+      <c r="I17" s="1"/>
+    </row>
+    <row r="18" spans="2:9" x14ac:dyDescent="0.4">
       <c r="C18">
         <v>13000</v>
       </c>
       <c r="D18" s="3">
+        <f t="shared" si="2"/>
+        <v>305694.64383541199</v>
+      </c>
+      <c r="E18" s="3">
         <f t="shared" si="0"/>
-        <v>305694.64383541199</v>
-      </c>
-      <c r="E18" s="3">
+        <v>247.82703188926791</v>
+      </c>
+      <c r="F18" s="7">
+        <f t="shared" si="1"/>
+        <v>11.537789271616548</v>
+      </c>
+      <c r="G18" s="8">
         <v>121344.56621300505</v>
       </c>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-    </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="H18" s="1"/>
+      <c r="I18" s="1"/>
+    </row>
+    <row r="19" spans="2:9" x14ac:dyDescent="0.4">
       <c r="C19">
         <v>14000</v>
       </c>
       <c r="D19" s="3">
+        <f t="shared" si="2"/>
+        <v>329209.61643813603</v>
+      </c>
+      <c r="E19" s="3">
         <f t="shared" si="0"/>
-        <v>329209.61643813603</v>
-      </c>
-      <c r="E19" s="3">
+        <v>266.89064972690397</v>
+      </c>
+      <c r="F19" s="7">
+        <f t="shared" si="1"/>
+        <v>12.425311523279362</v>
+      </c>
+      <c r="G19" s="8">
         <v>130424.39365381806</v>
       </c>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-    </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="H19" s="1"/>
+      <c r="I19" s="1"/>
+    </row>
+    <row r="20" spans="2:9" x14ac:dyDescent="0.4">
       <c r="C20">
         <v>15000</v>
       </c>
       <c r="D20" s="3">
+        <f t="shared" si="2"/>
+        <v>352724.58904086001</v>
+      </c>
+      <c r="E20" s="3">
         <f t="shared" si="0"/>
-        <v>352724.58904086001</v>
-      </c>
-      <c r="E20" s="3">
+        <v>285.95426756453992</v>
+      </c>
+      <c r="F20" s="7">
+        <f t="shared" si="1"/>
+        <v>13.312833774942174</v>
+      </c>
+      <c r="G20" s="8">
         <v>140645.20979357499</v>
       </c>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
-    </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="H20" s="1"/>
+      <c r="I20" s="1"/>
+    </row>
+    <row r="21" spans="2:9" x14ac:dyDescent="0.4">
       <c r="C21">
         <v>16000</v>
       </c>
       <c r="D21" s="3">
+        <f t="shared" si="2"/>
+        <v>376239.56164358399</v>
+      </c>
+      <c r="E21" s="3">
         <f t="shared" si="0"/>
-        <v>376239.56164358399</v>
-      </c>
-      <c r="E21" s="3">
+        <v>305.01788540217592</v>
+      </c>
+      <c r="F21" s="7">
+        <f t="shared" si="1"/>
+        <v>14.200356026604984</v>
+      </c>
+      <c r="G21" s="8">
         <v>149838.83143944858</v>
       </c>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
-    </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.35">
+      <c r="H21" s="1"/>
+      <c r="I21" s="1"/>
+    </row>
+    <row r="22" spans="2:9" x14ac:dyDescent="0.4">
       <c r="B22" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C22" s="3">
         <v>16785.730584030498</v>
       </c>
       <c r="D22" s="3">
+        <f t="shared" si="2"/>
+        <v>394715.99480018351</v>
+      </c>
+      <c r="E22" s="3">
         <f t="shared" si="0"/>
-        <v>394715.99480018351</v>
-      </c>
-      <c r="E22" s="3">
+        <v>319.9967529794759</v>
+      </c>
+      <c r="F22" s="7">
+        <f t="shared" si="1"/>
+        <v>14.89770940374407</v>
+      </c>
+      <c r="G22" s="8">
         <v>158104.1957609462</v>
       </c>
-      <c r="F22" s="1"/>
-      <c r="G22" s="1"/>
+      <c r="H22" s="1"/>
+      <c r="I22" s="1"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="E1:G1"/>
+    <mergeCell ref="G1:I1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{44889D92-5C1B-43B6-BE00-3D23C35CC93C}">
   <dimension ref="A1:Q39"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
   <cols>
-    <col min="1" max="1" width="8.7265625" customWidth="1"/>
-    <col min="2" max="3" width="11.81640625" customWidth="1"/>
-    <col min="4" max="4" width="22.26953125" customWidth="1"/>
-    <col min="5" max="5" width="28.81640625" customWidth="1"/>
-    <col min="6" max="6" width="26.90625" customWidth="1"/>
+    <col min="1" max="1" width="8.69140625" customWidth="1"/>
+    <col min="2" max="3" width="11.84375" customWidth="1"/>
+    <col min="4" max="4" width="22.23046875" customWidth="1"/>
+    <col min="5" max="5" width="28.84375" customWidth="1"/>
+    <col min="6" max="6" width="26.921875" customWidth="1"/>
     <col min="7" max="7" width="14" customWidth="1"/>
-    <col min="8" max="8" width="20.08984375" customWidth="1"/>
-    <col min="9" max="9" width="21.54296875" customWidth="1"/>
-    <col min="10" max="10" width="18.453125" customWidth="1"/>
-    <col min="11" max="11" width="18.81640625" customWidth="1"/>
+    <col min="8" max="8" width="20.07421875" customWidth="1"/>
+    <col min="9" max="9" width="21.53515625" customWidth="1"/>
+    <col min="10" max="10" width="18.4609375" customWidth="1"/>
+    <col min="11" max="11" width="18.84375" customWidth="1"/>
     <col min="12" max="12" width="22" customWidth="1"/>
-    <col min="13" max="13" width="22.54296875" customWidth="1"/>
-    <col min="14" max="14" width="25.36328125" customWidth="1"/>
-    <col min="15" max="15" width="19.1796875" customWidth="1"/>
-    <col min="16" max="16" width="28.6328125" customWidth="1"/>
-    <col min="17" max="17" width="16.26953125" style="3" customWidth="1"/>
+    <col min="13" max="13" width="22.53515625" customWidth="1"/>
+    <col min="14" max="14" width="25.3828125" customWidth="1"/>
+    <col min="15" max="15" width="19.15234375" customWidth="1"/>
+    <col min="16" max="16" width="28.61328125" customWidth="1"/>
+    <col min="17" max="17" width="16.23046875" style="3" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q1" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
+      <c r="A2" t="s">
         <v>18</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="Q1" s="5" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>19</v>
       </c>
       <c r="B2">
         <v>0</v>
@@ -1330,12 +3609,12 @@
         <v>0.70492795036996803</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B3">
         <v>0</v>
@@ -1384,12 +3663,12 @@
         <v>0.73773470848030298</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B4">
         <v>0</v>
@@ -1438,12 +3717,12 @@
         <v>1.0667868110000001</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B5">
         <v>0</v>
@@ -1492,12 +3771,12 @@
         <v>0.99424925925483998</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B6">
         <v>0</v>
@@ -1546,12 +3825,12 @@
         <v>0.93243811712477798</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B7">
         <v>5</v>
@@ -1600,9 +3879,9 @@
         <v>2.6406704469603199</v>
       </c>
     </row>
-    <row r="8" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B8">
         <v>5</v>
@@ -1651,9 +3930,9 @@
         <v>3.36954571208561</v>
       </c>
     </row>
-    <row r="9" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B9">
         <v>5</v>
@@ -1702,9 +3981,9 @@
         <v>4.8864727960722396</v>
       </c>
     </row>
-    <row r="10" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B10">
         <v>0</v>
@@ -1753,12 +4032,12 @@
         <v>0.88211430199999996</v>
       </c>
       <c r="Q10" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A11" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B11">
         <v>3</v>
@@ -1807,9 +4086,9 @@
         <v>1.7211299327173799</v>
       </c>
     </row>
-    <row r="12" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B12">
         <v>3</v>
@@ -1858,9 +4137,9 @@
         <v>1.45968753918303</v>
       </c>
     </row>
-    <row r="13" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B13">
         <v>3</v>
@@ -1909,9 +4188,9 @@
         <v>1.2818199310829099</v>
       </c>
     </row>
-    <row r="14" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B14">
         <v>3</v>
@@ -1960,9 +4239,9 @@
         <v>1.15734642471583</v>
       </c>
     </row>
-    <row r="15" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B15">
         <v>3</v>
@@ -2011,9 +4290,9 @@
         <v>1.06438923423513</v>
       </c>
     </row>
-    <row r="16" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B16">
         <v>3</v>
@@ -2062,9 +4341,9 @@
         <v>0.99711288227329198</v>
       </c>
     </row>
-    <row r="17" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B17">
         <v>0</v>
@@ -2113,12 +4392,12 @@
         <v>0.84334790223742195</v>
       </c>
       <c r="Q17" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B18">
         <v>0</v>
@@ -2167,12 +4446,12 @@
         <v>0.80833055138049104</v>
       </c>
       <c r="Q18" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B19">
         <v>0</v>
@@ -2221,12 +4500,12 @@
         <v>0.77781898176327602</v>
       </c>
       <c r="Q19" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B20">
         <v>0</v>
@@ -2275,12 +4554,12 @@
         <v>1.0400222475155101</v>
       </c>
       <c r="Q20" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B21">
         <v>0</v>
@@ -2329,12 +4608,12 @@
         <v>0.96998384928330195</v>
       </c>
       <c r="Q21" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B22">
         <v>0</v>
@@ -2383,12 +4662,12 @@
         <v>0.75491855067547597</v>
       </c>
       <c r="Q22" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B23">
         <v>0</v>
@@ -2437,12 +4716,12 @@
         <v>0.74298988026741397</v>
       </c>
       <c r="Q23" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B24">
         <v>0</v>
@@ -2491,12 +4770,12 @@
         <v>0.90984510301030797</v>
       </c>
       <c r="Q24" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="25" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B25">
         <v>0</v>
@@ -2545,12 +4824,12 @@
         <v>1.0717494293005001</v>
       </c>
       <c r="Q25" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.35">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B26">
         <v>0</v>
@@ -2599,12 +4878,12 @@
         <v>0.85971724445347397</v>
       </c>
       <c r="Q26" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B27">
         <v>0</v>
@@ -2653,12 +4932,12 @@
         <v>0.85971724445347397</v>
       </c>
       <c r="Q27" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B28">
         <v>0</v>
@@ -2707,12 +4986,12 @@
         <v>0.85971724445347397</v>
       </c>
       <c r="Q28" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="29" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B29">
         <v>0</v>
@@ -2761,12 +5040,12 @@
         <v>0.85637371278832397</v>
       </c>
       <c r="Q29" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B30">
         <v>0</v>
@@ -2815,12 +5094,12 @@
         <v>0.75177719391388198</v>
       </c>
       <c r="Q30" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="31" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B31">
         <v>0</v>
@@ -2869,12 +5148,12 @@
         <v>0.75177719391388198</v>
       </c>
       <c r="Q31" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B32">
         <v>0</v>
@@ -2923,12 +5202,12 @@
         <v>0.75177719391388198</v>
       </c>
       <c r="Q32" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="33" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B33">
         <v>0</v>
@@ -2977,12 +5256,12 @@
         <v>0.74951278418953005</v>
       </c>
       <c r="Q33" s="3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="34" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B34">
         <v>0</v>
@@ -3031,12 +5310,12 @@
         <v>0.86242976776195501</v>
       </c>
       <c r="Q34" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B35">
         <v>0</v>
@@ -3083,12 +5362,12 @@
         <v>0.82464177024617602</v>
       </c>
       <c r="Q35" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B36">
         <v>0</v>
@@ -3137,12 +5416,12 @@
         <v>0.78982525667983905</v>
       </c>
       <c r="Q36" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A37" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B37">
         <v>0</v>
@@ -3191,12 +5470,12 @@
         <v>0.76093473943346901</v>
       </c>
       <c r="Q37" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="38" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="38" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B38">
         <v>0</v>
@@ -3245,12 +5524,12 @@
         <v>0.73935121897885603</v>
       </c>
       <c r="Q38" s="3" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="39" spans="1:17" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" hidden="1" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B39">
         <v>0</v>
@@ -3299,7 +5578,7 @@
         <v>0.71757732056978696</v>
       </c>
       <c r="Q39" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
